--- a/planilhas/outputs/Categorizados.xlsx
+++ b/planilhas/outputs/Categorizados.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\lucas-silva\auto_shopee\planilhas\outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAFDABE-2CD6-42B4-A67F-AF179B5955F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,48 +25,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="1040">
-  <si>
-    <t xml:space="preserve">FITAS E  ADESIVOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA IMPERMEABILIZANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRAGENS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIVERSOS UD (UTILIDADES DOMESTICAS)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="1042">
+  <si>
+    <t>FITAS E  ADESIVOS</t>
+  </si>
+  <si>
+    <t>FITA IMPERMEABILIZANTES</t>
+  </si>
+  <si>
+    <t>FERRAGENS</t>
+  </si>
+  <si>
+    <t>DIVERSOS UD (UTILIDADES DOMESTICAS)</t>
   </si>
   <si>
     <t xml:space="preserve">COLAS </t>
   </si>
   <si>
-    <t xml:space="preserve">PINTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOMOTIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELÉTRICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIDRAULICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PISOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUBRIFICANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRAMENTAS MANUAIS</t>
+    <t>PINTURA</t>
+  </si>
+  <si>
+    <t>AUTOMOTIVA</t>
+  </si>
+  <si>
+    <t>ELÉTRICA</t>
+  </si>
+  <si>
+    <t>HIDRAULICA</t>
+  </si>
+  <si>
+    <t>PISOS</t>
+  </si>
+  <si>
+    <t>LUBRIFICANTES</t>
+  </si>
+  <si>
+    <t>FERRAMENTAS MANUAIS</t>
   </si>
   <si>
     <t xml:space="preserve">FERRAMENTAS MANUAIS ACESSÓRIOS </t>
   </si>
   <si>
-    <t xml:space="preserve">FERRAMENTAS ELETRICA E ACESSORIOS</t>
+    <t>FERRAMENTAS ELETRICA E ACESSORIOS</t>
   </si>
   <si>
     <t xml:space="preserve">PARAFUSOS </t>
@@ -70,148 +75,148 @@
     <t xml:space="preserve">MASSAS </t>
   </si>
   <si>
-    <t xml:space="preserve">BANHEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUVEIROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OUTROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPERMEABILIZANTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PILHAS E BATEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTENAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUFOS CALHAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONEXÕES AGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONEXÕES ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGRO JARDIM E PISCINAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORROSIVOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVA E CADEADOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADAS</t>
+    <t>BANHEIRO</t>
+  </si>
+  <si>
+    <t>EPI</t>
+  </si>
+  <si>
+    <t>CHUVEIROS</t>
+  </si>
+  <si>
+    <t>OUTROS</t>
+  </si>
+  <si>
+    <t>IMPERMEABILIZANTES</t>
+  </si>
+  <si>
+    <t>PILHAS E BATEIRAS</t>
+  </si>
+  <si>
+    <t>TELHAS</t>
+  </si>
+  <si>
+    <t>ANTENAS</t>
+  </si>
+  <si>
+    <t>RUFOS CALHAS</t>
+  </si>
+  <si>
+    <t>CONEXÕES AGUA</t>
+  </si>
+  <si>
+    <t>CONEXÕES ESGOTO</t>
+  </si>
+  <si>
+    <t>AGRO JARDIM E PISCINAS</t>
+  </si>
+  <si>
+    <t>PIAS</t>
+  </si>
+  <si>
+    <t>CORROSIVOS</t>
+  </si>
+  <si>
+    <t>TRAVA E CADEADOS</t>
+  </si>
+  <si>
+    <t>TOMADAS</t>
   </si>
   <si>
     <t xml:space="preserve">FITA DUREX </t>
   </si>
   <si>
-    <t xml:space="preserve">FITAS TIRA TRINCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLDANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRODEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATIDA DE PEDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CORRUGADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO CAIXA D'AGUA</t>
+    <t>FITAS TIRA TRINCA</t>
+  </si>
+  <si>
+    <t>ROLDANA</t>
+  </si>
+  <si>
+    <t>KRODEC</t>
+  </si>
+  <si>
+    <t>COLA BRANCA</t>
+  </si>
+  <si>
+    <t>ROLO</t>
+  </si>
+  <si>
+    <t>BATIDA DE PEDRA</t>
+  </si>
+  <si>
+    <t>LUVA CORRUGADO</t>
+  </si>
+  <si>
+    <t>FILTRO CAIXA D'AGUA</t>
   </si>
   <si>
     <t xml:space="preserve">ESPATULA SILICONE REJUNTE </t>
   </si>
   <si>
-    <t xml:space="preserve">GRAFITE EM PÓ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOLDA TUBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLITRIZ GOODYEAR ANG 71/4 1100W 220V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO HERC</t>
+    <t>GRAFITE EM PÓ</t>
+  </si>
+  <si>
+    <t>SACHO</t>
+  </si>
+  <si>
+    <t>SOLDA TUBO</t>
+  </si>
+  <si>
+    <t>POLITRIZ GOODYEAR ANG 71/4 1100W 220V</t>
+  </si>
+  <si>
+    <t>BUCHA</t>
+  </si>
+  <si>
+    <t>CIMENTO</t>
+  </si>
+  <si>
+    <t>ASSENTO HERC</t>
   </si>
   <si>
     <t xml:space="preserve">CAPACETE </t>
   </si>
   <si>
-    <t xml:space="preserve">BRACO CHUVEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIO CABO PATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PILHA ALCALINA</t>
+    <t>BRACO CHUVEIRO</t>
+  </si>
+  <si>
+    <t>FIO CABO PATCH</t>
+  </si>
+  <si>
+    <t>OTTO</t>
+  </si>
+  <si>
+    <t>PILHA ALCALINA</t>
   </si>
   <si>
     <t xml:space="preserve">CONJUNTO VEDACAO </t>
   </si>
   <si>
-    <t xml:space="preserve">ANTENA UHF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAL VIRGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANQUE RORATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO LINHAÇA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAÇANETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILUMI CONJUNTO</t>
+    <t>ANTENA UHF</t>
+  </si>
+  <si>
+    <t>RUFO</t>
+  </si>
+  <si>
+    <t>CURVA 3/4</t>
+  </si>
+  <si>
+    <t>JOELHO ESGOTO</t>
+  </si>
+  <si>
+    <t>CAL VIRGEM</t>
+  </si>
+  <si>
+    <t>TANQUE RORATO</t>
+  </si>
+  <si>
+    <t>OLEO LINHAÇA</t>
+  </si>
+  <si>
+    <t>MAÇANETA</t>
+  </si>
+  <si>
+    <t>ILUMI CONJUNTO</t>
   </si>
   <si>
     <t xml:space="preserve">FITA CREPE </t>
@@ -220,64 +225,64 @@
     <t xml:space="preserve">DENVERFITA  </t>
   </si>
   <si>
-    <t xml:space="preserve">MANCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA CONTATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA PLASTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAFON</t>
+    <t>MANCAL</t>
+  </si>
+  <si>
+    <t>RAQUETE</t>
+  </si>
+  <si>
+    <t>COLA CONTATO</t>
+  </si>
+  <si>
+    <t>EXTENSOR</t>
+  </si>
+  <si>
+    <t>MASSA PLASTICA</t>
+  </si>
+  <si>
+    <t>PLAFON</t>
   </si>
   <si>
     <t xml:space="preserve">IBIRA SUPORTE DRENAGEM </t>
   </si>
   <si>
-    <t xml:space="preserve">ALICATE NIVELADOR PISO/PAREDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WD-40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORCADO</t>
+    <t>ALICATE NIVELADOR PISO/PAREDE</t>
+  </si>
+  <si>
+    <t>WD-40</t>
+  </si>
+  <si>
+    <t>FORCADO</t>
   </si>
   <si>
     <t xml:space="preserve">LÁPIS </t>
   </si>
   <si>
-    <t xml:space="preserve">SOPRADOR TERMICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO DRYWALL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REJUNTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO SANITARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESISTENCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLACA SINALIZADORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADITIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATERIA</t>
+    <t>SOPRADOR TERMICO</t>
+  </si>
+  <si>
+    <t>PARAFUSO DRYWALL</t>
+  </si>
+  <si>
+    <t>REJUNTE</t>
+  </si>
+  <si>
+    <t>ASSENTO SANITARIO</t>
+  </si>
+  <si>
+    <t>COLETE</t>
+  </si>
+  <si>
+    <t>RESISTENCIA</t>
+  </si>
+  <si>
+    <t>PLACA SINALIZADORA</t>
+  </si>
+  <si>
+    <t>ADITIVO</t>
+  </si>
+  <si>
+    <t>BATERIA</t>
   </si>
   <si>
     <t xml:space="preserve">TELHA </t>
@@ -289,88 +294,88 @@
     <t xml:space="preserve">ACESSÓRIOS </t>
   </si>
   <si>
-    <t xml:space="preserve">TEE 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESGUICHO REVOLVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIA FIBRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SODA CAUSTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA JARDIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODULO TRAMONTINA</t>
+    <t>TEE 11/2</t>
+  </si>
+  <si>
+    <t>TE ESGOTO</t>
+  </si>
+  <si>
+    <t>ESGUICHO REVOLVER</t>
+  </si>
+  <si>
+    <t>PIA FIBRA</t>
+  </si>
+  <si>
+    <t>SODA CAUSTICA</t>
+  </si>
+  <si>
+    <t>TORNEIRA JARDIM</t>
+  </si>
+  <si>
+    <t>MODULO TRAMONTINA</t>
   </si>
   <si>
     <t xml:space="preserve">FITA EMBALAGEM </t>
   </si>
   <si>
-    <t xml:space="preserve">FITA AUTO ADESIVA</t>
+    <t>FITA AUTO ADESIVA</t>
   </si>
   <si>
     <t xml:space="preserve">FITA PERFURADA </t>
   </si>
   <si>
-    <t xml:space="preserve">MATA CUPIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEKBOND COLA INSTANTANEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CATALISADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFLETOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRESSURIZADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORTADOR PISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAMPEADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANETA</t>
+    <t>MATA CUPIM</t>
+  </si>
+  <si>
+    <t>TEKBOND COLA INSTANTANEA</t>
+  </si>
+  <si>
+    <t>GARFO</t>
+  </si>
+  <si>
+    <t>CATALISADOR</t>
+  </si>
+  <si>
+    <t>REFLETOR</t>
+  </si>
+  <si>
+    <t>PRESSURIZADOR</t>
+  </si>
+  <si>
+    <t>CORTADOR PISO</t>
+  </si>
+  <si>
+    <t>GRAXA</t>
+  </si>
+  <si>
+    <t>GRAMPEADOR</t>
+  </si>
+  <si>
+    <t>CANETA</t>
   </si>
   <si>
     <t xml:space="preserve">MAKITA </t>
   </si>
   <si>
-    <t xml:space="preserve">PARAFUSO CHIPBOARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GESSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA DESCARGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASCARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUVEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELASTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEDACIT</t>
+    <t>PARAFUSO CHIPBOARD</t>
+  </si>
+  <si>
+    <t>GESSO</t>
+  </si>
+  <si>
+    <t>CAIXA DESCARGA</t>
+  </si>
+  <si>
+    <t>MASCARA</t>
+  </si>
+  <si>
+    <t>CHUVEIRO</t>
+  </si>
+  <si>
+    <t>ELASTICO</t>
+  </si>
+  <si>
+    <t>VEDACIT</t>
   </si>
   <si>
     <r>
@@ -390,224 +395,224 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PANASONIC</t>
+      <t>PANASONIC</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">CUMEEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR METAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE CALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMENDA TRAMONTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIA INOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPA PEDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO LATAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPELHO TRAMONTINA</t>
+    <t>CUMEEIRA</t>
+  </si>
+  <si>
+    <t>CONECTOR METAL</t>
+  </si>
+  <si>
+    <t>SUPORTE CALHA</t>
+  </si>
+  <si>
+    <t>TE 11/2</t>
+  </si>
+  <si>
+    <t>CURVA ESGOTO</t>
+  </si>
+  <si>
+    <t>EMENDA TRAMONTINA</t>
+  </si>
+  <si>
+    <t>PIA INOX</t>
+  </si>
+  <si>
+    <t>LIMPA PEDRA</t>
+  </si>
+  <si>
+    <t>CADEADO LATAO</t>
+  </si>
+  <si>
+    <t>ESPELHO TRAMONTINA</t>
   </si>
   <si>
     <t xml:space="preserve">FITA ISOLANTE </t>
   </si>
   <si>
-    <t xml:space="preserve">FITAS ALUMÍNIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTONEIRA MOVEIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAVATINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA MADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRINCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THINNER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMPADA</t>
+    <t>FITAS ALUMÍNIO</t>
+  </si>
+  <si>
+    <t>CANTONEIRA MOVEIS</t>
+  </si>
+  <si>
+    <t>LAVATINA</t>
+  </si>
+  <si>
+    <t>COLA MADEIRA</t>
+  </si>
+  <si>
+    <t>TRINCHA</t>
+  </si>
+  <si>
+    <t>THINNER</t>
+  </si>
+  <si>
+    <t>LAMPADA</t>
   </si>
   <si>
     <t xml:space="preserve">ENGATE </t>
   </si>
   <si>
-    <t xml:space="preserve">MARTELO BORRACHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUBRIFICANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PE CABRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAMPO</t>
+    <t>MARTELO BORRACHA</t>
+  </si>
+  <si>
+    <t>LUBRIFICANTE</t>
+  </si>
+  <si>
+    <t>PE CABRA</t>
+  </si>
+  <si>
+    <t>GRAMPO</t>
   </si>
   <si>
     <t xml:space="preserve">FURADEIRA </t>
   </si>
   <si>
-    <t xml:space="preserve">CHUMBADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA CORRIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESPIRADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQUECEDOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANUNCIADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENVER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMENDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BICO UNIAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUBA INOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERJA LIMPADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTA CADEADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO TRAMONTINA</t>
+    <t>CHUMBADOR</t>
+  </si>
+  <si>
+    <t>MASSA CORRIDA</t>
+  </si>
+  <si>
+    <t>BACIA</t>
+  </si>
+  <si>
+    <t>RESPIRADOR</t>
+  </si>
+  <si>
+    <t>AQUECEDOR</t>
+  </si>
+  <si>
+    <t>ANUNCIADOR</t>
+  </si>
+  <si>
+    <t>DENVER</t>
+  </si>
+  <si>
+    <t>TABUA</t>
+  </si>
+  <si>
+    <t>EMENDA</t>
+  </si>
+  <si>
+    <t>CALHA</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL</t>
+  </si>
+  <si>
+    <t>LUVA ESGOTO</t>
+  </si>
+  <si>
+    <t>BICO UNIAO</t>
+  </si>
+  <si>
+    <t>CUBA INOX</t>
+  </si>
+  <si>
+    <t>FERJA LIMPADOR</t>
+  </si>
+  <si>
+    <t>PORTA CADEADO</t>
+  </si>
+  <si>
+    <t>CONJUNTO TRAMONTINA</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLA FACE </t>
   </si>
   <si>
-    <t xml:space="preserve">DRYKO FITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTONEIRA PRATELEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RALINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL COLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPRAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUARAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECEPTACULO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VENTOSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTICORROSIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOMBA VERTICAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELETRODO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA MARMORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCA TORNEADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARGAMASSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPA CHUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRAÇADEIRA P/ CANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIKA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SARRAFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE ANTENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALHA ZINCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTILIT LUVA AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNCAO ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESGUICHO PADRAO</t>
+    <t>DRYKO FITA</t>
+  </si>
+  <si>
+    <t>CANTONEIRA PRATELEIRA</t>
+  </si>
+  <si>
+    <t>RALINHO</t>
+  </si>
+  <si>
+    <t>REFIL COLA</t>
+  </si>
+  <si>
+    <t>SPRAY</t>
+  </si>
+  <si>
+    <t>AGUARAZ</t>
+  </si>
+  <si>
+    <t>RECEPTACULO</t>
+  </si>
+  <si>
+    <t>SPUD</t>
+  </si>
+  <si>
+    <t>VENTOSA</t>
+  </si>
+  <si>
+    <t>ANTICORROSIVO</t>
+  </si>
+  <si>
+    <t>BOMBA VERTICAL</t>
+  </si>
+  <si>
+    <t>ELETRODO</t>
+  </si>
+  <si>
+    <t>SERRA MARMORE</t>
+  </si>
+  <si>
+    <t>PORCA TORNEADA</t>
+  </si>
+  <si>
+    <t>ARGAMASSA</t>
+  </si>
+  <si>
+    <t>VASO</t>
+  </si>
+  <si>
+    <t>CAPA CHUVA</t>
+  </si>
+  <si>
+    <t>DUCHA</t>
+  </si>
+  <si>
+    <t>ABRAÇADEIRA P/ CANO</t>
+  </si>
+  <si>
+    <t>SIKA</t>
+  </si>
+  <si>
+    <t>SARRAFO</t>
+  </si>
+  <si>
+    <t>SUPORTE ANTENA</t>
+  </si>
+  <si>
+    <t>CALHA ZINCO</t>
+  </si>
+  <si>
+    <t>MULTILIT LUVA AZUL</t>
+  </si>
+  <si>
+    <t>JUNCAO ESGOTO</t>
+  </si>
+  <si>
+    <t>ESGUICHO PADRAO</t>
   </si>
   <si>
     <t xml:space="preserve">PIA SINTETICA </t>
   </si>
   <si>
-    <t xml:space="preserve">DIABO VERDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHO CHATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEC PLACA</t>
+    <t>DIABO VERDE</t>
+  </si>
+  <si>
+    <t>FECHO CHATO</t>
+  </si>
+  <si>
+    <t>MEC PLACA</t>
   </si>
   <si>
     <t xml:space="preserve">SILVER TAPE </t>
@@ -616,400 +621,400 @@
     <t xml:space="preserve">TELA P/ TRINCA </t>
   </si>
   <si>
-    <t xml:space="preserve">SUPORTE PRATELEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESENTUPIDOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA JUNTA DIESEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAXI RUBBER PRIMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERFONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO DE LIGAÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALHA AÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASELINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA FERRAMENTA</t>
+    <t>SUPORTE PRATELEIRA</t>
+  </si>
+  <si>
+    <t>DESENTUPIDOR</t>
+  </si>
+  <si>
+    <t>COLA JUNTA DIESEL</t>
+  </si>
+  <si>
+    <t>BROXA</t>
+  </si>
+  <si>
+    <t>MAXI RUBBER PRIMER</t>
+  </si>
+  <si>
+    <t>INTERFONE</t>
+  </si>
+  <si>
+    <t>TUBO DE LIGAÇÃO</t>
+  </si>
+  <si>
+    <t>PALHA AÇO</t>
+  </si>
+  <si>
+    <t>VASELINA</t>
+  </si>
+  <si>
+    <t>CAIXA FERRAMENTA</t>
   </si>
   <si>
     <t xml:space="preserve">PNEU </t>
   </si>
   <si>
-    <t xml:space="preserve">MARTELETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARUELA ZINC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCELANA PISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAVATORIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ÓCULOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRAÇADEIRA NYLON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIAPOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONTALETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIVISOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALHA FORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTRO ESFERA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REDUCAO ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANQUE PLASTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESINFETANTE CREO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHADURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO RADIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA ANTIDERRAPANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA TELADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTONEIRA ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RATOEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REMOVEDOR FERRUGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTA FIBRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SIFAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTALIDER GRAFITE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORTADOR DE VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMARA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PISTOLA COLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REBITE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIMASSA USO GERAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA DE APOIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA MAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTIRRESPINGO SOLDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRYKOPRIMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECEPTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE EXTERNO ZINCO PLATIBANDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA PLUG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA RETENCAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA ARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIA ACO INOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONVERTEDOR DE FERRUGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO PADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPELHO RADIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA ZEBRADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA VEDATUDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE BRASFORT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGULHA P/ FOGÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPÓXI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TINTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADESIVO LAMINAÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRAMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA LAVATORIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPACADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO MAQUINA</t>
+    <t>MARTELETE</t>
+  </si>
+  <si>
+    <t>ARUELA ZINC</t>
+  </si>
+  <si>
+    <t>PORCELANA PISO</t>
+  </si>
+  <si>
+    <t>LAVATORIO</t>
+  </si>
+  <si>
+    <t>ÓCULOS</t>
+  </si>
+  <si>
+    <t>ABRAÇADEIRA NYLON</t>
+  </si>
+  <si>
+    <t>VIAPOL</t>
+  </si>
+  <si>
+    <t>PONTALETE</t>
+  </si>
+  <si>
+    <t>DIVISOR</t>
+  </si>
+  <si>
+    <t>CALHA FORTE</t>
+  </si>
+  <si>
+    <t>REGISTRO ESFERA</t>
+  </si>
+  <si>
+    <t>REDUCAO ESGOTO</t>
+  </si>
+  <si>
+    <t>TANQUE PLASTICO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE CREO</t>
+  </si>
+  <si>
+    <t>FECHADURA</t>
+  </si>
+  <si>
+    <t>CONJUNTO RADIAL</t>
+  </si>
+  <si>
+    <t>FITA ANTIDERRAPANTE</t>
+  </si>
+  <si>
+    <t>FITA TELADA</t>
+  </si>
+  <si>
+    <t>CANTONEIRA ALUMINIO</t>
+  </si>
+  <si>
+    <t>RATOEIRA</t>
+  </si>
+  <si>
+    <t>REMOVEDOR FERRUGEM</t>
+  </si>
+  <si>
+    <t>MANTA FIBRA</t>
+  </si>
+  <si>
+    <t>SOQUETE</t>
+  </si>
+  <si>
+    <t>SIFAO</t>
+  </si>
+  <si>
+    <t>JOELHEIRA</t>
+  </si>
+  <si>
+    <t>JUNTALIDER GRAFITE</t>
+  </si>
+  <si>
+    <t>CORTADOR DE VIDRO</t>
+  </si>
+  <si>
+    <t>CAMARA</t>
+  </si>
+  <si>
+    <t>PISTOLA COLA</t>
+  </si>
+  <si>
+    <t>REBITE</t>
+  </si>
+  <si>
+    <t>MULTIMASSA USO GERAL</t>
+  </si>
+  <si>
+    <t>BARRA DE APOIO</t>
+  </si>
+  <si>
+    <t>LUVA MAO</t>
+  </si>
+  <si>
+    <t>ANTIRRESPINGO SOLDA</t>
+  </si>
+  <si>
+    <t>DRYKOPRIMER</t>
+  </si>
+  <si>
+    <t>RECEPTOR</t>
+  </si>
+  <si>
+    <t>SUPORTE EXTERNO ZINCO PLATIBANDA</t>
+  </si>
+  <si>
+    <t>KRONA PLUG</t>
+  </si>
+  <si>
+    <t>VALVULA RETENCAO</t>
+  </si>
+  <si>
+    <t>PENEIRA ARO</t>
+  </si>
+  <si>
+    <t>PIA ACO INOX</t>
+  </si>
+  <si>
+    <t>CONVERTEDOR DE FERRUGEM</t>
+  </si>
+  <si>
+    <t>CADEADO PADO</t>
+  </si>
+  <si>
+    <t>ESPELHO RADIAL</t>
+  </si>
+  <si>
+    <t>FITA ZEBRADA</t>
+  </si>
+  <si>
+    <t>FITA VEDATUDO</t>
+  </si>
+  <si>
+    <t>SUPORTE BRASFORT</t>
+  </si>
+  <si>
+    <t>AGULHA P/ FOGÃO</t>
+  </si>
+  <si>
+    <t>EPÓXI</t>
+  </si>
+  <si>
+    <t>TINTA</t>
+  </si>
+  <si>
+    <t>ADESIVO LAMINAÇÃO</t>
+  </si>
+  <si>
+    <t>BARRAMENTO</t>
+  </si>
+  <si>
+    <t>VALVULA LAVATORIO</t>
+  </si>
+  <si>
+    <t>ESPACADOR</t>
+  </si>
+  <si>
+    <t>OLEO MAQUINA</t>
   </si>
   <si>
     <t xml:space="preserve">ESPATULA </t>
   </si>
   <si>
-    <t xml:space="preserve">CINTO FERRAMENTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERRO SOLDA</t>
+    <t>CINTO FERRAMENTAS</t>
+  </si>
+  <si>
+    <t>FERRO SOLDA</t>
   </si>
   <si>
     <t xml:space="preserve">PITÃO </t>
   </si>
   <si>
-    <t xml:space="preserve">VARANDAS E QUINTAIS SC 20KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMARIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABAFADOR DE RUIDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA VIDRACEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTA LIQUIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTENA EXT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.FORTE SUPORTE EXTERNO ZINCO 28 MOLDURA TORCIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTADOR CURTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA PLASTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TANQUE SINTETICO RORATO</t>
+    <t>VARANDAS E QUINTAIS SC 20KG</t>
+  </si>
+  <si>
+    <t>ARMARIO</t>
+  </si>
+  <si>
+    <t>ABAFADOR DE RUIDOS</t>
+  </si>
+  <si>
+    <t>MASSA VIDRACEIRO</t>
+  </si>
+  <si>
+    <t>MANTA LIQUIDA</t>
+  </si>
+  <si>
+    <t>ANTENA EXT</t>
+  </si>
+  <si>
+    <t>C.FORTE SUPORTE EXTERNO ZINCO 28 MOLDURA TORCIDO</t>
+  </si>
+  <si>
+    <t>ADAPTADOR CURTO</t>
+  </si>
+  <si>
+    <t>CAPS ESGOTO</t>
+  </si>
+  <si>
+    <t>PENEIRA PLASTICO</t>
+  </si>
+  <si>
+    <t>TANQUE SINTETICO RORATO</t>
   </si>
   <si>
     <t xml:space="preserve">REMOVEDOR DE FERRUGEM </t>
   </si>
   <si>
-    <t xml:space="preserve">CADEADO PAPAIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILUMI PLACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA MULTIUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTAO DOMESTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARALDITE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA MASSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA CANALETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA SABESP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIVELADOR PISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPA CONTATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPATULAS METAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABO MULTIMETRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPIRADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCAPULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA PRONTA ASSENT REVEST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOUCADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTETOR AUDITIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA CALAFETAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECPLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANTENA INTERNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA CURTA ESGOTO</t>
+    <t>CADEADO PAPAIZ</t>
+  </si>
+  <si>
+    <t>ILUMI PLACA</t>
+  </si>
+  <si>
+    <t>FITA MARROM</t>
+  </si>
+  <si>
+    <t>FITA MULTIUSO</t>
+  </si>
+  <si>
+    <t>DOBRADICA</t>
+  </si>
+  <si>
+    <t>PORTAO DOMESTICO</t>
+  </si>
+  <si>
+    <t>ARALDITE</t>
+  </si>
+  <si>
+    <t>LIXA MASSA</t>
+  </si>
+  <si>
+    <t>BOINA</t>
+  </si>
+  <si>
+    <t>SISTEMA CANALETA</t>
+  </si>
+  <si>
+    <t>CAIXA SABESP</t>
+  </si>
+  <si>
+    <t>NIVELADOR PISO</t>
+  </si>
+  <si>
+    <t>LIMPA CONTATO</t>
+  </si>
+  <si>
+    <t>ESPATULAS METAL</t>
+  </si>
+  <si>
+    <t>CABO MULTIMETRO</t>
+  </si>
+  <si>
+    <t>ASPIRADOR</t>
+  </si>
+  <si>
+    <t>ESCAPULA</t>
+  </si>
+  <si>
+    <t>MASSA PRONTA ASSENT REVEST</t>
+  </si>
+  <si>
+    <t>TOUCADOR</t>
+  </si>
+  <si>
+    <t>PROTETOR AUDITIVO</t>
+  </si>
+  <si>
+    <t>MASSA CALAFETAR</t>
+  </si>
+  <si>
+    <t>TECPLUS</t>
+  </si>
+  <si>
+    <t>ANTENA INTERNA</t>
+  </si>
+  <si>
+    <t>CAP 3/4</t>
+  </si>
+  <si>
+    <t>CURVA CURTA ESGOTO</t>
   </si>
   <si>
     <t xml:space="preserve">PULVERIZADOR </t>
   </si>
   <si>
-    <t xml:space="preserve">TANQUE SINTETICO GRAN N2 110X55 PRETO AJ RORATO</t>
+    <t>TANQUE SINTETICO GRAN N2 110X55 PRETO AJ RORATO</t>
   </si>
   <si>
     <t xml:space="preserve">REMOVEDOR COLA </t>
   </si>
   <si>
-    <t xml:space="preserve">CORRENTE SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILUMI ESPELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LORENZETTI FITA ISOLANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA ALTA FUSAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIBRA ABRASIVA LIMPEZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA AZULEJO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANDEIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GALVITE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXINHA LUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALHA DE ACO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SINGER OLEO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRENA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAPIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTIMETRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANCHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCELANA E PISO PISO EXTERNO CINZA 20KG PLACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT FIXACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CINTO DELTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESENGRAXANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIABIT</t>
+    <t>CORRENTE SOLDAVEL</t>
+  </si>
+  <si>
+    <t>ILUMI ESPELHO</t>
+  </si>
+  <si>
+    <t>LORENZETTI FITA ISOLANTE</t>
+  </si>
+  <si>
+    <t>FITA ALTA FUSAO</t>
+  </si>
+  <si>
+    <t>PREGO</t>
+  </si>
+  <si>
+    <t>FIBRA ABRASIVA LIMPEZA</t>
+  </si>
+  <si>
+    <t>COLA AZULEJO</t>
+  </si>
+  <si>
+    <t>BANDEIA</t>
+  </si>
+  <si>
+    <t>GALVITE</t>
+  </si>
+  <si>
+    <t>CAIXINHA LUZ</t>
+  </si>
+  <si>
+    <t>TUBO</t>
+  </si>
+  <si>
+    <t>PALHA DE ACO</t>
+  </si>
+  <si>
+    <t>SINGER OLEO</t>
+  </si>
+  <si>
+    <t>TRENA</t>
+  </si>
+  <si>
+    <t>LAPIS</t>
+  </si>
+  <si>
+    <t>MULTIMETRO</t>
+  </si>
+  <si>
+    <t>GANCHO</t>
+  </si>
+  <si>
+    <t>PORCELANA E PISO PISO EXTERNO CINZA 20KG PLACA</t>
+  </si>
+  <si>
+    <t>KIT FIXACAO</t>
+  </si>
+  <si>
+    <t>CINTO DELTA</t>
+  </si>
+  <si>
+    <t>DESENGRAXANTE</t>
+  </si>
+  <si>
+    <t>VIABIT</t>
   </si>
   <si>
     <r>
@@ -1029,329 +1034,329 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">COAXIAL</t>
+      <t>COAXIAL</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">LUVA 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDA PULVERIZADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TARGETA RCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODULO MECTRONIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA ANTIDERRAP 50MMX05M TEKBOND PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTA ASFALTICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAME</t>
+    <t>LUVA 3/4</t>
+  </si>
+  <si>
+    <t>COTOVELO ESGOTO</t>
+  </si>
+  <si>
+    <t>EDA PULVERIZADOR</t>
+  </si>
+  <si>
+    <t>TARGETA RCA</t>
+  </si>
+  <si>
+    <t>MODULO MECTRONIC</t>
+  </si>
+  <si>
+    <t>FITA ANTIDERRAP 50MMX05M TEKBOND PRETO</t>
+  </si>
+  <si>
+    <t>MANTA ASFALTICA</t>
+  </si>
+  <si>
+    <t>ARAME</t>
   </si>
   <si>
     <t xml:space="preserve">AREJADOR </t>
   </si>
   <si>
-    <t xml:space="preserve">VEDACALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTOPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERMINAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA D'AGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUNHA NIVELADORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO LUBRIFICANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LINHA PEDREIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL MACARICOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPERIMETRO DIGITAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO ABROCANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCELANA E PISO PISO INTERNO CINZA 20KG PLACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO FIXACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODIZIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTTO PRIMER MANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA LUVA LL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS DE ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENROLADOR MANGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVA PORTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO MECTRONIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITA ISOLANTE LC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEDATUDO FITA ADESIVA ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCORA PINO LISO AÇÃO INDIRETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CESTINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PU40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROMA PINCEL ARTESANATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARRA CABO BATERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR BORNE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRESSURIZADOR CAIXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAXA SPRAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESEMPENADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAS MACARICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RABO QUENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO MAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCELANA E PISO PISO EXTERNO BRANCO 20KG PLACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA ACOPLADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAPATO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPACITOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRIMER MANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA MOSQUITEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVA PORTAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO PIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASILIT FITA ADESIVA ALUMINIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXA FIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA CORREIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA VINIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAÇAMBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABO CHUPETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONDUITE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA BOIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO MULTIUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALICATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAS BUTANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TESTE VOLTAGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO SEXTAVADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO SANITÁRIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAPIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE LLL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO VISITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NYLON CORTAR GRAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHO CADEADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAMONTINA MODULO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANCORA TELA P/ TRINCA FIBRA VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TACHINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEDRA AFIAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA FIXA TUDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTA VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIO SOM/LUSTRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACESS P/CAIXA ROCO CONJUNTO FIXACAO 1244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO DESENGRIPANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSÃO CAVADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOMBA D'AGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCA BORBOLETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTOR FIXACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABO REDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEUTROL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CORRER ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA TRANÇADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO STAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAMONTINA PLACA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIRATRINCA FITA P/ TRINCA 005X03M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTICADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA FIXA ESPELHO/CUBA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRACADEIRA NYLON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABO FLEX</t>
+    <t>VEDACALHA</t>
+  </si>
+  <si>
+    <t>CORANTE</t>
+  </si>
+  <si>
+    <t>ESTOPA</t>
+  </si>
+  <si>
+    <t>TERMINAL</t>
+  </si>
+  <si>
+    <t>CAIXA D'AGUA</t>
+  </si>
+  <si>
+    <t>CUNHA NIVELADORA</t>
+  </si>
+  <si>
+    <t>OLEO LUBRIFICANTE</t>
+  </si>
+  <si>
+    <t>LINHA PEDREIRO</t>
+  </si>
+  <si>
+    <t>REFIL MACARICOS</t>
+  </si>
+  <si>
+    <t>AMPERIMETRO DIGITAL</t>
+  </si>
+  <si>
+    <t>PARAFUSO ABROCANTE</t>
+  </si>
+  <si>
+    <t>PORCELANA E PISO PISO INTERNO CINZA 20KG PLACA</t>
+  </si>
+  <si>
+    <t>PARAFUSO FIXACAO</t>
+  </si>
+  <si>
+    <t>BOTA</t>
+  </si>
+  <si>
+    <t>RODIZIO</t>
+  </si>
+  <si>
+    <t>OTTO PRIMER MANTA</t>
+  </si>
+  <si>
+    <t>KRONA LUVA LL</t>
+  </si>
+  <si>
+    <t>CAPS DE ESGOTO</t>
+  </si>
+  <si>
+    <t>ENROLADOR MANGUEIRA</t>
+  </si>
+  <si>
+    <t>TRAVA PORTA</t>
+  </si>
+  <si>
+    <t>CONJUNTO MECTRONIC</t>
+  </si>
+  <si>
+    <t>FITA ISOLANTE LC</t>
+  </si>
+  <si>
+    <t>VEDATUDO FITA ADESIVA ALUMINIO</t>
+  </si>
+  <si>
+    <t>ANCORA PINO LISO AÇÃO INDIRETA</t>
+  </si>
+  <si>
+    <t>CESTINHA</t>
+  </si>
+  <si>
+    <t>PU40</t>
+  </si>
+  <si>
+    <t>ROMA PINCEL ARTESANATO</t>
+  </si>
+  <si>
+    <t>GARRA CABO BATERIA</t>
+  </si>
+  <si>
+    <t>CONECTOR BORNE</t>
+  </si>
+  <si>
+    <t>PRESSURIZADOR CAIXA</t>
+  </si>
+  <si>
+    <t>GRAXA SPRAY</t>
+  </si>
+  <si>
+    <t>DESEMPENADEIRA</t>
+  </si>
+  <si>
+    <t>GAS MACARICO</t>
+  </si>
+  <si>
+    <t>RABO QUENTE</t>
+  </si>
+  <si>
+    <t>PARAFUSO MAQ</t>
+  </si>
+  <si>
+    <t>PORCELANA E PISO PISO EXTERNO BRANCO 20KG PLACA</t>
+  </si>
+  <si>
+    <t>CAIXA ACOPLADA</t>
+  </si>
+  <si>
+    <t>SAPATO</t>
+  </si>
+  <si>
+    <t>CAPACITOR</t>
+  </si>
+  <si>
+    <t>PRIMER MANTA</t>
+  </si>
+  <si>
+    <t>LUVA 11/2</t>
+  </si>
+  <si>
+    <t>TEE ESGOTO</t>
+  </si>
+  <si>
+    <t>TELA MOSQUITEIRO</t>
+  </si>
+  <si>
+    <t>TRAVA PORTAO</t>
+  </si>
+  <si>
+    <t>CONJUNTO PIAL</t>
+  </si>
+  <si>
+    <t>BRASILIT FITA ADESIVA ALUMINIO</t>
+  </si>
+  <si>
+    <t>FIXA FIO</t>
+  </si>
+  <si>
+    <t>CAIXA CORREIO</t>
+  </si>
+  <si>
+    <t>COLA VINIL</t>
+  </si>
+  <si>
+    <t>CAÇAMBA</t>
+  </si>
+  <si>
+    <t>CABO CHUPETA</t>
+  </si>
+  <si>
+    <t>CONDUITE</t>
+  </si>
+  <si>
+    <t>TORNEIRA BOIA</t>
+  </si>
+  <si>
+    <t>OLEO MULTIUSO</t>
+  </si>
+  <si>
+    <t>ALICATE</t>
+  </si>
+  <si>
+    <t>GAS BUTANO</t>
+  </si>
+  <si>
+    <t>TESTE VOLTAGEM</t>
+  </si>
+  <si>
+    <t>PARAFUSO SEXTAVADO</t>
+  </si>
+  <si>
+    <t>PARAFUSO SANITÁRIO</t>
+  </si>
+  <si>
+    <t>CAPAS</t>
+  </si>
+  <si>
+    <t>CORDA</t>
+  </si>
+  <si>
+    <t>CHAPIX</t>
+  </si>
+  <si>
+    <t>TE LLL</t>
+  </si>
+  <si>
+    <t>COTOVELO VISITA</t>
+  </si>
+  <si>
+    <t>NYLON CORTAR GRAMA</t>
+  </si>
+  <si>
+    <t>FECHO CADEADO</t>
+  </si>
+  <si>
+    <t>TRAMONTINA MODULO</t>
+  </si>
+  <si>
+    <t>ANCORA TELA P/ TRINCA FIBRA VIDRO</t>
+  </si>
+  <si>
+    <t>TACHINHA</t>
+  </si>
+  <si>
+    <t>PEDRA AFIAR</t>
+  </si>
+  <si>
+    <t>COLA FIXA TUDO</t>
+  </si>
+  <si>
+    <t>VERNIZ</t>
+  </si>
+  <si>
+    <t>MANTA VIDRO</t>
+  </si>
+  <si>
+    <t>FIO SOM/LUSTRE</t>
+  </si>
+  <si>
+    <t>ACESS P/CAIXA ROCO CONJUNTO FIXACAO 1244</t>
+  </si>
+  <si>
+    <t>OLEO DESENGRIPANTE</t>
+  </si>
+  <si>
+    <t>SERRORTE</t>
+  </si>
+  <si>
+    <t>EXTENSÃO CAVADEIRA</t>
+  </si>
+  <si>
+    <t>BOMBA D'AGUA</t>
+  </si>
+  <si>
+    <t>PORCA BORBOLETA</t>
+  </si>
+  <si>
+    <t>CONJUNTOR FIXACAO</t>
+  </si>
+  <si>
+    <t>BOTINA</t>
+  </si>
+  <si>
+    <t>CABO REDE</t>
+  </si>
+  <si>
+    <t>NEUTROL</t>
+  </si>
+  <si>
+    <t>TE AZUL</t>
+  </si>
+  <si>
+    <t>LUVA CORRER ESGOTO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA TRANÇADA</t>
+  </si>
+  <si>
+    <t>CADEADO STAM</t>
+  </si>
+  <si>
+    <t>TRAMONTINA PLACA</t>
+  </si>
+  <si>
+    <t>TIRATRINCA FITA P/ TRINCA 005X03M</t>
+  </si>
+  <si>
+    <t>ESTICADOR</t>
+  </si>
+  <si>
+    <t>COLA FIXA ESPELHO/CUBA</t>
+  </si>
+  <si>
+    <t>SELADOR</t>
+  </si>
+  <si>
+    <t>ABRACADEIRA NYLON</t>
+  </si>
+  <si>
+    <t>CABO FLEX</t>
   </si>
   <si>
     <t xml:space="preserve">DUCHA HIGENICA  </t>
   </si>
   <si>
-    <t xml:space="preserve">LIMPA CONTATO SPRAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERROTE IRWIN GESSO</t>
+    <t>LIMPA CONTATO SPRAY</t>
+  </si>
+  <si>
+    <t>SERROTE IRWIN GESSO</t>
   </si>
   <si>
     <r>
@@ -1371,278 +1376,278 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GARAPEIRA</t>
+      <t>GARAPEIRA</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ESMERILHADEIRA ANGULAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO CHIPBORD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO OVAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVENTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOCO VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELA LUVA RETENCAO ESGOTO 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO SILVANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAMONTINA CONJUNTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GANCHO REDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASSOURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPUMA EXPANSIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MASSA POLIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIO CABO AUTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTROS E ACABAMENTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE GRIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANÇA CHAMAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESMERILHADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW FIX PARAFUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO ALMOFADADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEIA UMBRO</t>
+    <t>ESMERILHADEIRA ANGULAR</t>
+  </si>
+  <si>
+    <t>PARAFUSO CHIPBORD</t>
+  </si>
+  <si>
+    <t>ASSENTO OVAL</t>
+  </si>
+  <si>
+    <t>AVENTAL</t>
+  </si>
+  <si>
+    <t>BLOCO VIDRO</t>
+  </si>
+  <si>
+    <t>LUVA AZUL</t>
+  </si>
+  <si>
+    <t>ESTRELA LUVA RETENCAO ESGOTO 100</t>
+  </si>
+  <si>
+    <t>REGADOR</t>
+  </si>
+  <si>
+    <t>CADEADO SILVANA</t>
+  </si>
+  <si>
+    <t>TRAMONTINA CONJUNTO</t>
+  </si>
+  <si>
+    <t>GANCHO REDE</t>
+  </si>
+  <si>
+    <t>VASSOURA</t>
+  </si>
+  <si>
+    <t>ESPUMA EXPANSIVA</t>
+  </si>
+  <si>
+    <t>FUNDO</t>
+  </si>
+  <si>
+    <t>MASSA POLIR</t>
+  </si>
+  <si>
+    <t>FIO CABO AUTO</t>
+  </si>
+  <si>
+    <t>REGISTROS E ACABAMENTOS</t>
+  </si>
+  <si>
+    <t>CHAVE GRIFO</t>
+  </si>
+  <si>
+    <t>LANÇA CHAMAS</t>
+  </si>
+  <si>
+    <t>ESMERILHADEIRA</t>
+  </si>
+  <si>
+    <t>NEW FIX PARAFUSO</t>
+  </si>
+  <si>
+    <t>ASSENTO ALMOFADADO</t>
+  </si>
+  <si>
+    <t>MEIA UMBRO</t>
   </si>
   <si>
     <t xml:space="preserve">PAPEL SULFITE </t>
   </si>
   <si>
-    <t xml:space="preserve">ADAPTADOR FLANGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA VIVEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAVA LARETAL PORTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO ARIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GONZO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELATRINCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT PINTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERROX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR WAGO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEDA ROSCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLHER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL P/ MACARICOS E FOGAREIROS ETANIZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FURADEIRA/PARAFUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORCA SEXTAVADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPELEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGOTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAPEL TOALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA LONGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA CRISTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO GOLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEC CONJUNTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPA VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SILICONE ACETICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QUEROSENE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HASTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOQUEADOR DE AR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARTELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO CAVADEIRA TRADO</t>
+    <t>ADAPTADOR FLANGE</t>
+  </si>
+  <si>
+    <t>TELA VIVEIRO</t>
+  </si>
+  <si>
+    <t>TRAVA LARETAL PORTA</t>
+  </si>
+  <si>
+    <t>CONJUNTO ARIA</t>
+  </si>
+  <si>
+    <t>GONZO</t>
+  </si>
+  <si>
+    <t>RODO</t>
+  </si>
+  <si>
+    <t>SELATRINCA</t>
+  </si>
+  <si>
+    <t>KIT PINTURA</t>
+  </si>
+  <si>
+    <t>FERROX</t>
+  </si>
+  <si>
+    <t>CONECTOR WAGO</t>
+  </si>
+  <si>
+    <t>VEDA ROSCA</t>
+  </si>
+  <si>
+    <t>COLHER</t>
+  </si>
+  <si>
+    <t>REFIL P/ MACARICOS E FOGAREIROS ETANIZ</t>
+  </si>
+  <si>
+    <t>FURADEIRA/PARAFUSO</t>
+  </si>
+  <si>
+    <t>PORCA SEXTAVADO</t>
+  </si>
+  <si>
+    <t>PAPELEIRA</t>
+  </si>
+  <si>
+    <t>MANGOTE</t>
+  </si>
+  <si>
+    <t>PAPEL TOALHA</t>
+  </si>
+  <si>
+    <t>CURVA LONGA</t>
+  </si>
+  <si>
+    <t>MANGUEIRA CRISTAL</t>
+  </si>
+  <si>
+    <t>CADEADO GOLD</t>
+  </si>
+  <si>
+    <t>MEC CONJUNTO</t>
+  </si>
+  <si>
+    <t>LIMPA VIDRO</t>
+  </si>
+  <si>
+    <t>SILICONE ACETICO</t>
+  </si>
+  <si>
+    <t>CAL</t>
+  </si>
+  <si>
+    <t>QUEROSENE</t>
+  </si>
+  <si>
+    <t>HASTE</t>
+  </si>
+  <si>
+    <t>BLOQUEADOR DE AR</t>
+  </si>
+  <si>
+    <t>MARTELO</t>
+  </si>
+  <si>
+    <t>EXTENSAO CAVADEIRA TRADO</t>
   </si>
   <si>
     <t xml:space="preserve">PISTOLA SILICONE </t>
   </si>
   <si>
-    <t xml:space="preserve">ARRUELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUVEIRINHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CINTO SEGURANÇA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACO AREIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BESTWAY REPARO INFLAVEIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASFORT CADEADO BIKE CHAVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPELHO MECTRONIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTONEIRA</t>
+    <t>ARRUELA</t>
+  </si>
+  <si>
+    <t>CHUVEIRINHO</t>
+  </si>
+  <si>
+    <t>CINTO SEGURANÇA</t>
+  </si>
+  <si>
+    <t>SACO AREIA</t>
+  </si>
+  <si>
+    <t>JOELHO AZUL</t>
+  </si>
+  <si>
+    <t>BESTWAY REPARO INFLAVEIS</t>
+  </si>
+  <si>
+    <t>BRASFORT CADEADO BIKE CHAVE</t>
+  </si>
+  <si>
+    <t>ESPELHO MECTRONIC</t>
+  </si>
+  <si>
+    <t>CANTONEIRA</t>
   </si>
   <si>
     <t xml:space="preserve">LAMPADA FOGÃO	</t>
   </si>
   <si>
-    <t xml:space="preserve">COLA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAXI RUBBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PASSA FIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RALO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARRETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL PISTOLA GRANDE SILICONE 1K EM BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PISTOLA P/ SILICONE BIVOLT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO ROSCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAMPA BORRACHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA TRICOTADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITILHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA LR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA TELAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO SEGREDO STAM 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X RADIAL SIMPLES CAIXA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PÉ FOGÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEK BOND SILICONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZARCÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPIR DE PO WAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARM PRESS BOW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARCO SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL PISTOLA PEQUENA SILICONE 1K EM BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA CIRCULAR SKILL</t>
+    <t>COLA BRANCO</t>
+  </si>
+  <si>
+    <t>LONA</t>
+  </si>
+  <si>
+    <t>MAXI RUBBER</t>
+  </si>
+  <si>
+    <t>PASSA FIO</t>
+  </si>
+  <si>
+    <t>RALO</t>
+  </si>
+  <si>
+    <t>MARRETA</t>
+  </si>
+  <si>
+    <t>REFIL PISTOLA GRANDE SILICONE 1K EM BARRA</t>
+  </si>
+  <si>
+    <t>PISTOLA P/ SILICONE BIVOLT</t>
+  </si>
+  <si>
+    <t>PARAFUSO ROSCA</t>
+  </si>
+  <si>
+    <t>TAMPA BORRACHA</t>
+  </si>
+  <si>
+    <t>LUVA TRICOTADA</t>
+  </si>
+  <si>
+    <t>FITILHO</t>
+  </si>
+  <si>
+    <t>LUVA LR</t>
+  </si>
+  <si>
+    <t>PENEIRA TELAS</t>
+  </si>
+  <si>
+    <t>CADEADO SEGREDO STAM 25</t>
+  </si>
+  <si>
+    <t>SISTEMA X RADIAL SIMPLES CAIXA BRANCO</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA</t>
+  </si>
+  <si>
+    <t>PÉ FOGÃO</t>
+  </si>
+  <si>
+    <t>TEK BOND SILICONE</t>
+  </si>
+  <si>
+    <t>ZARCÃO</t>
+  </si>
+  <si>
+    <t>ASPIR DE PO WAP</t>
+  </si>
+  <si>
+    <t>ARM PRESS BOW</t>
+  </si>
+  <si>
+    <t>ARCO SERRA</t>
+  </si>
+  <si>
+    <t>REFIL PISTOLA PEQUENA SILICONE 1K EM BARRA</t>
+  </si>
+  <si>
+    <t>SERRA CIRCULAR SKILL</t>
   </si>
   <si>
     <r>
@@ -1662,38 +1667,38 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PHILIPS</t>
+      <t>PHILIPS</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">TAMPA TANQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA DELTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VENTILADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO LR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA NYLON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADEADO SEGREDO STAM 40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X RADIAL 2 TOMADAS  CAIXA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA ROSCADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA PU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALDE</t>
+    <t>TAMPA TANQUE</t>
+  </si>
+  <si>
+    <t>LUVA DELTA</t>
+  </si>
+  <si>
+    <t>VENTILADOR</t>
+  </si>
+  <si>
+    <t>JOELHO LR</t>
+  </si>
+  <si>
+    <t>TELA NYLON</t>
+  </si>
+  <si>
+    <t>CADEADO SEGREDO STAM 40</t>
+  </si>
+  <si>
+    <t>SISTEMA X RADIAL 2 TOMADAS  CAIXA BRANCO</t>
+  </si>
+  <si>
+    <t>BARRA ROSCADA</t>
+  </si>
+  <si>
+    <t>COLA PU</t>
+  </si>
+  <si>
+    <t>BALDE</t>
   </si>
   <si>
     <t xml:space="preserve">MASSA PLASTICO </t>
@@ -1702,70 +1707,70 @@
     <t xml:space="preserve">CAIXA DE PASSAGEM </t>
   </si>
   <si>
-    <t xml:space="preserve">VEDANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENXADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO FURADEIRA</t>
+    <t>VEDANTE</t>
+  </si>
+  <si>
+    <t>ENXADA</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO FURADEIRA</t>
   </si>
   <si>
     <t xml:space="preserve">ICDER REBOLO </t>
   </si>
   <si>
-    <t xml:space="preserve">PARAFUSO FRANCES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT BANHEIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA SANRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EKILON LINHA NYLON P/ PESCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA TE LLL 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIAO TORNEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPELHO CEGO ILUMI SLIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA ZINC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGULADOR GAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUREPOXI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA SECO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EDA MACACO HIDRAULICO  TONELADAS JACARE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISJUNTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLAS CANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO SERRA MARMORE MAKITA</t>
+    <t>PARAFUSO FRANCES</t>
+  </si>
+  <si>
+    <t>KIT BANHEIRO</t>
+  </si>
+  <si>
+    <t>LUVA SANRO</t>
+  </si>
+  <si>
+    <t>EKILON LINHA NYLON P/ PESCA</t>
+  </si>
+  <si>
+    <t>KRONA TE LLL 11/2</t>
+  </si>
+  <si>
+    <t>UNIAO TORNEIRA</t>
+  </si>
+  <si>
+    <t>ESPELHO CEGO ILUMI SLIM</t>
+  </si>
+  <si>
+    <t>BARRA ZINC</t>
+  </si>
+  <si>
+    <t>REGULADOR GAS</t>
+  </si>
+  <si>
+    <t>DUREPOXI</t>
+  </si>
+  <si>
+    <t>LIXA SECO</t>
+  </si>
+  <si>
+    <t>EDA MACACO HIDRAULICO  TONELADAS JACARE</t>
+  </si>
+  <si>
+    <t>DISJUNTOR</t>
+  </si>
+  <si>
+    <t>COLAS CANO</t>
+  </si>
+  <si>
+    <t>RAMADA</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO SERRA MARMORE MAKITA</t>
   </si>
   <si>
     <t xml:space="preserve">NYLON ROCADEIRA	</t>
   </si>
   <si>
-    <t xml:space="preserve">LUZARTE COLUNA</t>
+    <t>LUZARTE COLUNA</t>
   </si>
   <si>
     <r>
@@ -1785,494 +1790,494 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">KALIPSO</t>
+      <t>KALIPSO</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ALCOOL GEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE RRR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA GALVANIZADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAMONTINA TOMADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INCA ABRACADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUMERO COLONIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA HENKEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA FERRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIO BICOLOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENTRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA SIFONADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PÁ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO ALLEN/SEXTAVADO MAKITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT COMPRESSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO METASUL ALMOFADADO OVAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA IMBAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTA SANFONADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA CAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTADOR INTERNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODULO MECTRONIC TOMADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INCA RSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT GÁS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPER BONDER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA TATU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITAQUA DILUENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE DISJUNTOR</t>
+    <t>ALCOOL GEL</t>
+  </si>
+  <si>
+    <t>TE RRR</t>
+  </si>
+  <si>
+    <t>TELA GALVANIZADO</t>
+  </si>
+  <si>
+    <t>TRAMONTINA TOMADA</t>
+  </si>
+  <si>
+    <t>INCA ABRACADEIRA</t>
+  </si>
+  <si>
+    <t>NUMERO COLONIAL</t>
+  </si>
+  <si>
+    <t>COLA HENKEL</t>
+  </si>
+  <si>
+    <t>LIXA FERRO</t>
+  </si>
+  <si>
+    <t>FIO BICOLOR</t>
+  </si>
+  <si>
+    <t>CENTRI</t>
+  </si>
+  <si>
+    <t>CAIXA SIFONADA</t>
+  </si>
+  <si>
+    <t>PÁ</t>
+  </si>
+  <si>
+    <t>PARAFUSO ALLEN/SEXTAVADO MAKITA</t>
+  </si>
+  <si>
+    <t>KIT COMPRESSOR</t>
+  </si>
+  <si>
+    <t>ASSENTO METASUL ALMOFADADO OVAL</t>
+  </si>
+  <si>
+    <t>LUVA IMBAT</t>
+  </si>
+  <si>
+    <t>PORTA SANFONADA</t>
+  </si>
+  <si>
+    <t>KRONA CAP</t>
+  </si>
+  <si>
+    <t>ADAPTADOR INTERNO</t>
+  </si>
+  <si>
+    <t>MODULO MECTRONIC TOMADA</t>
+  </si>
+  <si>
+    <t>INCA RSF</t>
+  </si>
+  <si>
+    <t>KIT GÁS</t>
+  </si>
+  <si>
+    <t>SUPER BONDER</t>
+  </si>
+  <si>
+    <t>LIXA TATU</t>
+  </si>
+  <si>
+    <t>ITAQUA DILUENTE</t>
+  </si>
+  <si>
+    <t>SUPORTE DISJUNTOR</t>
   </si>
   <si>
     <t xml:space="preserve">SIFÃO 	</t>
   </si>
   <si>
-    <t xml:space="preserve">PICARETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROCA MAKITA WIDEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO BITS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO TIGRE OVAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA RASPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLASTICO BOLHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTILIT ADAPTADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASFORT FIO NYLON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRACADEIRA RSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOGÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA SELANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESMALTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FC GARRA P/ CABO BATERIA 100A GRANDE PRETO/VERMELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBTURADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT MAKITA JOGO PONTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCO</t>
+    <t>PICARETA</t>
+  </si>
+  <si>
+    <t>BROCA MAKITA WIDEA</t>
+  </si>
+  <si>
+    <t>JOGO BITS</t>
+  </si>
+  <si>
+    <t>ASSENTO TIGRE OVAL</t>
+  </si>
+  <si>
+    <t>LUVA RASPA</t>
+  </si>
+  <si>
+    <t>PLASTICO BOLHA</t>
+  </si>
+  <si>
+    <t>MULTILIT ADAPTADOR</t>
+  </si>
+  <si>
+    <t>BRASFORT FIO NYLON</t>
+  </si>
+  <si>
+    <t>ABRACADEIRA RSF</t>
+  </si>
+  <si>
+    <t>FOGÃO</t>
+  </si>
+  <si>
+    <t>COLA SELANTE</t>
+  </si>
+  <si>
+    <t>ESMALTE</t>
+  </si>
+  <si>
+    <t>FC GARRA P/ CABO BATERIA 100A GRANDE PRETO/VERMELHO</t>
+  </si>
+  <si>
+    <t>OBTURADOR</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>KIT MAKITA JOGO PONTAS</t>
+  </si>
+  <si>
+    <t>DISCO</t>
   </si>
   <si>
     <t xml:space="preserve">ALPHA DUCHA HIGIENICA REGISTRO METAL </t>
   </si>
   <si>
-    <t xml:space="preserve">LUVA EMBORRACHADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTA MADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS PLASTILIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLASTCOR TELA PLASTICA TAPUME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRAMONTINA INTERNA 1P S/PLACA 10A/250V BRANCO 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA SILVANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPER COLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUA RAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNEED GARRA P/ CABO BATERIA 10A MEDIO VERMELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAXINHA LUZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAPA FURO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALAVANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO DE ESCOVAS DE CARVAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSENTO ATLAS ALMOFADADO BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CONSTRUÇÃO DELTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACO ENTULHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIAO INTERNA REBOUCAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X RADIAL 1INT SIMPLES CAIXA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIGUELAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTAO FRANCES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA SILICONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNEED GARRA P/ CABO BATERIA 10A MEDIO PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLAFONIER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA SABESP/TAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHIBANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARVAO FURADEIRA MAKITA 8419/6016 C133G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISTURADOR DE TINTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUCHA HIGIENICA FERTAK BRANCO 7041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA  COMFORT KALIPSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXADOR PORTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA ARO MADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X RADIAL 2 INTERRUPTORES SIMPLES CAIXA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA ROSCA GALVANIZADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECEPTOR DE TV DIGITAL AQUARIO</t>
+    <t>LUVA EMBORRACHADA</t>
+  </si>
+  <si>
+    <t>PORTA MADEIRA</t>
+  </si>
+  <si>
+    <t>CAPS PLASTILIT</t>
+  </si>
+  <si>
+    <t>PLASTCOR TELA PLASTICA TAPUME</t>
+  </si>
+  <si>
+    <t>TRAMONTINA INTERNA 1P S/PLACA 10A/250V BRANCO 50</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA SILVANA</t>
+  </si>
+  <si>
+    <t>KIT PE</t>
+  </si>
+  <si>
+    <t>SUPER COLA</t>
+  </si>
+  <si>
+    <t>AGUA RAZ</t>
+  </si>
+  <si>
+    <t>INTERNEED GARRA P/ CABO BATERIA 10A MEDIO VERMELHO</t>
+  </si>
+  <si>
+    <t>CAXINHA LUZ</t>
+  </si>
+  <si>
+    <t>TAPA FURO</t>
+  </si>
+  <si>
+    <t>ALAVANCA</t>
+  </si>
+  <si>
+    <t>JOGO DE ESCOVAS DE CARVAO</t>
+  </si>
+  <si>
+    <t>BROCA</t>
+  </si>
+  <si>
+    <t>ASSENTO ATLAS ALMOFADADO BRANCO</t>
+  </si>
+  <si>
+    <t>LUVA CONSTRUÇÃO DELTA</t>
+  </si>
+  <si>
+    <t>SACO ENTULHO</t>
+  </si>
+  <si>
+    <t>JOELHO SOLDAVEL</t>
+  </si>
+  <si>
+    <t>UNIAO INTERNA REBOUCAS</t>
+  </si>
+  <si>
+    <t>SISTEMA X RADIAL 1INT SIMPLES CAIXA BRANCO</t>
+  </si>
+  <si>
+    <t>MIGUELAO</t>
+  </si>
+  <si>
+    <t>BOTAO FRANCES</t>
+  </si>
+  <si>
+    <t>COLA SILICONE</t>
+  </si>
+  <si>
+    <t>INTERNEED GARRA P/ CABO BATERIA 10A MEDIO PRETO</t>
+  </si>
+  <si>
+    <t>PLAFONIER</t>
+  </si>
+  <si>
+    <t>CAIXA SABESP/TAF</t>
+  </si>
+  <si>
+    <t>CHIBANCA</t>
+  </si>
+  <si>
+    <t>CARVAO FURADEIRA MAKITA 8419/6016 C133G</t>
+  </si>
+  <si>
+    <t>MISTURADOR DE TINTA</t>
+  </si>
+  <si>
+    <t>DUCHA HIGIENICA FERTAK BRANCO 7041</t>
+  </si>
+  <si>
+    <t>LUVA  COMFORT KALIPSO</t>
+  </si>
+  <si>
+    <t>FIXADOR PORTA</t>
+  </si>
+  <si>
+    <t>CURVA SOLDAVEL</t>
+  </si>
+  <si>
+    <t>PENEIRA ARO MADEIRA</t>
+  </si>
+  <si>
+    <t>SISTEMA X RADIAL 2 INTERRUPTORES SIMPLES CAIXA BRANCO</t>
+  </si>
+  <si>
+    <t>BARRA ROSCA GALVANIZADO</t>
+  </si>
+  <si>
+    <t>RECEPTOR DE TV DIGITAL AQUARIO</t>
   </si>
   <si>
     <t xml:space="preserve">AMANCO ADESIVO </t>
   </si>
   <si>
-    <t xml:space="preserve">PO XADREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUSIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA GORDURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARRINHO MAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO SERRA MARMORE MAKITA 4100NB C137G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO/CARVÃO CARBONPEÇAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATILHO HIGIBAN DUCHA HIGIENICA BRANCO/CROMADO SUPORTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CONSTRUCAO VE730 10 DELTA PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRINDE SQUEEZE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKATO JOELHO SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BICO ENGATE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X ILUMI 2 INTERRUPTORES SIMPLES 6A 6318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACANETA SILVANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA CARTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEDA CALHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LATEX ACRILICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA ILUMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA DE INSPEÇÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORQUES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO SERRA MARMORE MAKITA 4100H/5800 C138G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO DE ESCOVAS E PONTEIRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CONSTRUCAO VE730 09 DELTA PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASFORT BARBANTE DE ALGODAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENGATE MANGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPELHO ILUMI SLIM 4X4 CEGO 8305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INCA ABRACAD RSF (C)1/2X3/4 ( 100) (M GAS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CABIDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLA TIGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANDEIA PINTURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X ILUMI LUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLAS PVC</t>
+    <t>PO XADREZ</t>
+  </si>
+  <si>
+    <t>FUSIVEL</t>
+  </si>
+  <si>
+    <t>CAIXA GORDURA</t>
+  </si>
+  <si>
+    <t>CARRINHO MAO</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO SERRA MARMORE MAKITA 4100NB C137G</t>
+  </si>
+  <si>
+    <t>PARAFUSO/CARVÃO CARBONPEÇAS</t>
+  </si>
+  <si>
+    <t>GATILHO HIGIBAN DUCHA HIGIENICA BRANCO/CROMADO SUPORTE</t>
+  </si>
+  <si>
+    <t>LUVA CONSTRUCAO VE730 10 DELTA PLUS</t>
+  </si>
+  <si>
+    <t>BRINDE SQUEEZE</t>
+  </si>
+  <si>
+    <t>AKATO JOELHO SOLDAVEL</t>
+  </si>
+  <si>
+    <t>BICO ENGATE</t>
+  </si>
+  <si>
+    <t>SISTEMA X ILUMI 2 INTERRUPTORES SIMPLES 6A 6318</t>
+  </si>
+  <si>
+    <t>MACANETA SILVANA</t>
+  </si>
+  <si>
+    <t>CAIXA CARTA</t>
+  </si>
+  <si>
+    <t>VEDA CALHA</t>
+  </si>
+  <si>
+    <t>LATEX ACRILICA</t>
+  </si>
+  <si>
+    <t>SISTEMA ILUMI</t>
+  </si>
+  <si>
+    <t>CAIXA DE INSPEÇÃO</t>
+  </si>
+  <si>
+    <t>TORQUES</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO SERRA MARMORE MAKITA 4100H/5800 C138G</t>
+  </si>
+  <si>
+    <t>JOGO DE ESCOVAS E PONTEIRAS</t>
+  </si>
+  <si>
+    <t>LUVA CONSTRUCAO VE730 09 DELTA PLUS</t>
+  </si>
+  <si>
+    <t>BRASFORT BARBANTE DE ALGODAO</t>
+  </si>
+  <si>
+    <t>CAP SOLDAVEL</t>
+  </si>
+  <si>
+    <t>ENGATE MANGUEIRA</t>
+  </si>
+  <si>
+    <t>ESPELHO ILUMI SLIM 4X4 CEGO 8305</t>
+  </si>
+  <si>
+    <t>INCA ABRACAD RSF (C)1/2X3/4 ( 100) (M GAS)</t>
+  </si>
+  <si>
+    <t>CABIDE</t>
+  </si>
+  <si>
+    <t>COLA TIGRE</t>
+  </si>
+  <si>
+    <t>BANDEIA PINTURA</t>
+  </si>
+  <si>
+    <t>SISTEMA X ILUMI LUVA</t>
+  </si>
+  <si>
+    <t>COLAS PVC</t>
   </si>
   <si>
     <t xml:space="preserve">APLICADOR </t>
   </si>
   <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO FURADEIRA MAKITA6404/5 CB70 C184G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANDRIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA NBR WAVE KALIPSO AZUL/PRETO 09 G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTETOR SOLAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKATO CAP SOLDAVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA JARDIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X ILUMI LUVA BRANCO 6205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF METAIS ABRACADEIRA TIPO U B 3/4 100 J F METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA TANQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIPEGA SILICONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA AGUA</t>
+    <t>CARBONPEÇAS CARVAO FURADEIRA MAKITA6404/5 CB70 C184G</t>
+  </si>
+  <si>
+    <t>MANDRIL</t>
+  </si>
+  <si>
+    <t>LUVA NBR WAVE KALIPSO AZUL/PRETO 09 G</t>
+  </si>
+  <si>
+    <t>PROTETOR SOLAR</t>
+  </si>
+  <si>
+    <t>AKATO CAP SOLDAVEL</t>
+  </si>
+  <si>
+    <t>MANGUEIRA JARDIM</t>
+  </si>
+  <si>
+    <t>SISTEMA X ILUMI LUVA BRANCO 6205</t>
+  </si>
+  <si>
+    <t>JF METAIS ABRACADEIRA TIPO U B 3/4 100 J F METAIS</t>
+  </si>
+  <si>
+    <t>TORNEIRA TANQ</t>
+  </si>
+  <si>
+    <t>UNIPEGA SILICONE</t>
+  </si>
+  <si>
+    <t>LIXA AGUA</t>
   </si>
   <si>
     <t xml:space="preserve">CAIXA LUZ </t>
   </si>
   <si>
-    <t xml:space="preserve">CAIXA DE PASSAGEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO SERRA MARMORE DW/BD 301/3011 C185G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDS-PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA NBR WAVE KALIPSO AZUL/PRETO 10 XG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMENDA MANGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO PIAL POP 1 TOMADA 10A LGX030 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF METAIS ABRACADEIRA TIPO U E 1 1/2 100 J F METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOALHA MESA TERMICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPUMA POLIURETANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA MADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANALETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALHADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARVAO SERRA MARMORE MAKITA NHK9227 C188G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCOVA AÇO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO LL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASSOURA GRAMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONJUNTO PIAL POP 1 SIMPLES 1 TOMADA 10A LGX103 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF METAIS ABRACADEIRA TIPO U F 2 100 J F METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARRAFAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASCOREZ HENKEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LATEX QUARTZOLIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANNLUX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANEL BORRACHA</t>
+    <t>CAIXA DE PASSAGEM</t>
+  </si>
+  <si>
+    <t>NIVEL</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO SERRA MARMORE DW/BD 301/3011 C185G</t>
+  </si>
+  <si>
+    <t>SDS-PLUS</t>
+  </si>
+  <si>
+    <t>LUVA NBR WAVE KALIPSO AZUL/PRETO 10 XG</t>
+  </si>
+  <si>
+    <t>COTOVELO AZUL</t>
+  </si>
+  <si>
+    <t>EMENDA MANGUEIRA</t>
+  </si>
+  <si>
+    <t>CONJUNTO PIAL POP 1 TOMADA 10A LGX030 BRANCO</t>
+  </si>
+  <si>
+    <t>JF METAIS ABRACADEIRA TIPO U E 1 1/2 100 J F METAIS</t>
+  </si>
+  <si>
+    <t>TOALHA MESA TERMICA</t>
+  </si>
+  <si>
+    <t>ESPUMA POLIURETANO</t>
+  </si>
+  <si>
+    <t>LIXA MADEIRA</t>
+  </si>
+  <si>
+    <t>CANALETA</t>
+  </si>
+  <si>
+    <t>TALHADEIRA</t>
+  </si>
+  <si>
+    <t>CARVAO SERRA MARMORE MAKITA NHK9227 C188G</t>
+  </si>
+  <si>
+    <t>ESCOVA AÇO</t>
+  </si>
+  <si>
+    <t>JOELHO LL</t>
+  </si>
+  <si>
+    <t>VASSOURA GRAMA</t>
+  </si>
+  <si>
+    <t>CONJUNTO PIAL POP 1 SIMPLES 1 TOMADA 10A LGX103 BRANCO</t>
+  </si>
+  <si>
+    <t>JF METAIS ABRACADEIRA TIPO U F 2 100 J F METAIS</t>
+  </si>
+  <si>
+    <t>GARRAFAO</t>
+  </si>
+  <si>
+    <t>CASCOREZ HENKEL</t>
+  </si>
+  <si>
+    <t>LATEX QUARTZOLIT</t>
+  </si>
+  <si>
+    <t>ANNLUX</t>
+  </si>
+  <si>
+    <t>ANEL BORRACHA</t>
   </si>
   <si>
     <t xml:space="preserve">PONTEIRO </t>
   </si>
   <si>
-    <t xml:space="preserve">PARAFUSO ALLEN/SEXTAVADO MAKITA 5900 C18407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROCADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMANCO LUVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VEDACIT CUPINICIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF METAIS ABRACADEIRA TIPO U H 3 50 J F METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAP TORNEIRA</t>
+    <t>PARAFUSO ALLEN/SEXTAVADO MAKITA 5900 C18407</t>
+  </si>
+  <si>
+    <t>ROCADEIRA</t>
+  </si>
+  <si>
+    <t>AMANCO LUVA</t>
+  </si>
+  <si>
+    <t>VEDACIT CUPINICIDA</t>
+  </si>
+  <si>
+    <t>TOMADA</t>
+  </si>
+  <si>
+    <t>JF METAIS ABRACADEIRA TIPO U H 3 50 J F METAIS</t>
+  </si>
+  <si>
+    <t>GRAP TORNEIRA</t>
   </si>
   <si>
     <r>
@@ -2292,359 +2297,359 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">HENKEL</t>
+      <t>HENKEL</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">PAREDE NOVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONERTOR BORNE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA FORTLEV</t>
+    <t>PAREDE NOVA</t>
+  </si>
+  <si>
+    <t>CONERTOR BORNE</t>
+  </si>
+  <si>
+    <t>CAIXA FORTLEV</t>
   </si>
   <si>
     <t xml:space="preserve">ESCOVA AÇO 	</t>
   </si>
   <si>
-    <t xml:space="preserve">PARAFUSO ALLEN/SEXTAVADO MAKITA 4100 C8408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS CORR PLASTIK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA MM ARO MADEIRA  AREIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLUG MACHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JF METAIS ABRACADEIRA TIPO U J 4 50 J F METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CESTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXA CUBA/ESPELHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA BOSCH MASSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRUGADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA ENTRADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVADEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO PONTEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS FORTLEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARQUA MANGUEIRA MULTIUSO TRANÇADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADA EM BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA PRESSAO 35MM RETA JOMARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BRASLIDER SUPORTE BOTIJAO AZUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SILICONE INCOLOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA QUADRADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR INTERNEED PORCELANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORTLEV CAIXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRUMO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA COPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA FORLTEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARQUA MANGUEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO DE LINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA PRESSAO 35MM CURVA JOMARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPUMA DE POLIURETANO</t>
+    <t>PARAFUSO ALLEN/SEXTAVADO MAKITA 4100 C8408</t>
+  </si>
+  <si>
+    <t>FLAP</t>
+  </si>
+  <si>
+    <t>CAPS CORR PLASTIK</t>
+  </si>
+  <si>
+    <t>PENEIRA MM ARO MADEIRA  AREIA</t>
+  </si>
+  <si>
+    <t>PLUG MACHO</t>
+  </si>
+  <si>
+    <t>JF METAIS ABRACADEIRA TIPO U J 4 50 J F METAIS</t>
+  </si>
+  <si>
+    <t>CESTO</t>
+  </si>
+  <si>
+    <t>FIXA CUBA/ESPELHO</t>
+  </si>
+  <si>
+    <t>LIXA BOSCH MASSA</t>
+  </si>
+  <si>
+    <t>CORRUGADO</t>
+  </si>
+  <si>
+    <t>VALVULA ENTRADA</t>
+  </si>
+  <si>
+    <t>CAVADEIRA</t>
+  </si>
+  <si>
+    <t>JOGO PONTEIRA</t>
+  </si>
+  <si>
+    <t>CAPS FORTLEV</t>
+  </si>
+  <si>
+    <t>ARQUA MANGUEIRA MULTIUSO TRANÇADA</t>
+  </si>
+  <si>
+    <t>TOMADA EM BARRA</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA PRESSAO 35MM RETA JOMARCA</t>
+  </si>
+  <si>
+    <t>BRASLIDER SUPORTE BOTIJAO AZUL</t>
+  </si>
+  <si>
+    <t>SILICONE INCOLOR</t>
+  </si>
+  <si>
+    <t>PA QUADRADA</t>
+  </si>
+  <si>
+    <t>CONECTOR INTERNEED PORCELANA</t>
+  </si>
+  <si>
+    <t>FORTLEV CAIXA</t>
+  </si>
+  <si>
+    <t>PRUMO</t>
+  </si>
+  <si>
+    <t>SERRA COPO</t>
+  </si>
+  <si>
+    <t>LUVA FORLTEV</t>
+  </si>
+  <si>
+    <t>ARQUA MANGUEIRA</t>
+  </si>
+  <si>
+    <t>FILTRO DE LINHA</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA PRESSAO 35MM CURVA JOMARCA</t>
+  </si>
+  <si>
+    <t>VARAL</t>
+  </si>
+  <si>
+    <t>ESPUMA DE POLIURETANO</t>
   </si>
   <si>
     <t xml:space="preserve">PA BICO </t>
   </si>
   <si>
-    <t xml:space="preserve">LUMINARIA ALETADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRELHA REDONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE TORX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REBOLO DIAMANTADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA TIGRE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA FEIJAO 55 PLASTICO 10 TELAS MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINO MACHO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA PRESSAO 26MM CURVA JOMARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARIN SILICONE INCOLOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA DOBLEA FERRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR PORCELANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA AGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TESOURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA CIRCULAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMANCO NIPEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA MM ARO PLASTICO 55 AREIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FC EXTENSAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA PRESSAO 26MM RETA JOMARCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELATRINCAS GARIN BRANCO TUBO 450GR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAYERLACK MASSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENZEL TERMINAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA AMERICANA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAÇARICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONTEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO PLASTILIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENEIRA MM ARO PLASTICO 55 ARROZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINO PRENSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOBRADIÇA LEME ZINCADA LOTH 06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOALHA MESA TRANSPARENTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIPEGA SELANTE PU FLEXIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA NORTON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXLUX FIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA HIDROMETRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PULVEIZADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PONTA MONTADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIAO PLASTILIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA PLASTICO VIVEIRO 100X50 1/2 PRT NETTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTADOR FEMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INCA ABRACAD RSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASCOREZ EXTRA 1000GR HENKEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRONORTH RESINA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVANT LUMINARIA</t>
+    <t>LUMINARIA ALETADA</t>
+  </si>
+  <si>
+    <t>GRELHA REDONDO</t>
+  </si>
+  <si>
+    <t>CHAVE TORX</t>
+  </si>
+  <si>
+    <t>REBOLO DIAMANTADO</t>
+  </si>
+  <si>
+    <t>LUVA TIGRE</t>
+  </si>
+  <si>
+    <t>PENEIRA FEIJAO 55 PLASTICO 10 TELAS MM</t>
+  </si>
+  <si>
+    <t>PINO MACHO</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA PRESSAO 26MM CURVA JOMARCA</t>
+  </si>
+  <si>
+    <t>ESCADA</t>
+  </si>
+  <si>
+    <t>GARIN SILICONE INCOLOR</t>
+  </si>
+  <si>
+    <t>LIXA DOBLEA FERRO</t>
+  </si>
+  <si>
+    <t>CONECTOR PORCELANA</t>
+  </si>
+  <si>
+    <t>CAIXA AGUA</t>
+  </si>
+  <si>
+    <t>TESOURA</t>
+  </si>
+  <si>
+    <t>SERRA CIRCULAR</t>
+  </si>
+  <si>
+    <t>AMANCO NIPEL</t>
+  </si>
+  <si>
+    <t>PENEIRA MM ARO PLASTICO 55 AREIA</t>
+  </si>
+  <si>
+    <t>FC EXTENSAO</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA PRESSAO 26MM RETA JOMARCA</t>
+  </si>
+  <si>
+    <t>VELA</t>
+  </si>
+  <si>
+    <t>SELATRINCAS GARIN BRANCO TUBO 450GR</t>
+  </si>
+  <si>
+    <t>SAYERLACK MASSA</t>
+  </si>
+  <si>
+    <t>PENZEL TERMINAL</t>
+  </si>
+  <si>
+    <t>VÁLVULA AMERICANA</t>
+  </si>
+  <si>
+    <t>MAÇARICO</t>
+  </si>
+  <si>
+    <t>PONTEIRA</t>
+  </si>
+  <si>
+    <t>COTOVELO PLASTILIT</t>
+  </si>
+  <si>
+    <t>PENEIRA MM ARO PLASTICO 55 ARROZ</t>
+  </si>
+  <si>
+    <t>PINO PRENSA</t>
+  </si>
+  <si>
+    <t>DOBRADIÇA LEME ZINCADA LOTH 06</t>
+  </si>
+  <si>
+    <t>TOALHA MESA TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>UNIPEGA SELANTE PU FLEXIVEL</t>
+  </si>
+  <si>
+    <t>LIXA NORTON</t>
+  </si>
+  <si>
+    <t>FOXLUX FIO</t>
+  </si>
+  <si>
+    <t>CAIXA HIDROMETRO</t>
+  </si>
+  <si>
+    <t>PULVEIZADOR</t>
+  </si>
+  <si>
+    <t>PONTA MONTADA</t>
+  </si>
+  <si>
+    <t>UNIAO PLASTILIT</t>
+  </si>
+  <si>
+    <t>TELA PLASTICO VIVEIRO 100X50 1/2 PRT NETTE</t>
+  </si>
+  <si>
+    <t>ADAPTADOR FEMEA</t>
+  </si>
+  <si>
+    <t>INCA ABRACAD RSF</t>
+  </si>
+  <si>
+    <t>FACAO</t>
+  </si>
+  <si>
+    <t>CASCOREZ EXTRA 1000GR HENKEL</t>
+  </si>
+  <si>
+    <t>HYDRONORTH RESINA</t>
+  </si>
+  <si>
+    <t>AVANT LUMINARIA</t>
   </si>
   <si>
     <t xml:space="preserve"> REGISTRO GAVETA</t>
   </si>
   <si>
-    <t xml:space="preserve">BOMBA AR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REFIL PISTOLA  SILICONE EM BARRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPLE PLASTILT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TELA PLASTICO PINTINHO 100X50 1 PRETO NETTEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSÃO TECHNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TERMINAL ROCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASCOLA 85GR MONTA/FIXA HENKEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATLAS PINCEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIO TELEF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE ZAMAC CROMADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOCO ESPUMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARBONPEÇAS CARVAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA CROMADO EMA METAIS 1128X3/4 JARD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINO FEMEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE TV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARIN SILICONE 050G INCOLOR COLMEIA 12 GARI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGUARRAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SENSOR PRESENÇA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUMENTO TORNEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTILETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTADOR FURADEIRA P/ DISCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELA LIGA FACIL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA CROMADO JARDIM ESFERA 1/2 FERTAK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO LINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROLE TV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIPEGA SELANTE POLIURETANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA BOSCH AGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELETRODUTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA HYDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE SOQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCO BORRACHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE FORTLEV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAP TORNEIRA JARDIM ABS/PRETO 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNEED EXTENSÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GABINETE</t>
+    <t>BOMBA AR</t>
+  </si>
+  <si>
+    <t>REFIL PISTOLA  SILICONE EM BARRA</t>
+  </si>
+  <si>
+    <t>NIPLE PLASTILT</t>
+  </si>
+  <si>
+    <t>TELA PLASTICO PINTINHO 100X50 1 PRETO NETTEN</t>
+  </si>
+  <si>
+    <t>EXTENSÃO TECHNA</t>
+  </si>
+  <si>
+    <t>TERMINAL ROCO</t>
+  </si>
+  <si>
+    <t>CASCOLA 85GR MONTA/FIXA HENKEL</t>
+  </si>
+  <si>
+    <t>ATLAS PINCEL</t>
+  </si>
+  <si>
+    <t>FIO TELEF</t>
+  </si>
+  <si>
+    <t>TEE ZAMAC CROMADO</t>
+  </si>
+  <si>
+    <t>BLOCO ESPUMA</t>
+  </si>
+  <si>
+    <t>CARBONPEÇAS CARVAO</t>
+  </si>
+  <si>
+    <t>CAP MARROM</t>
+  </si>
+  <si>
+    <t>TORNEIRA CROMADO EMA METAIS 1128X3/4 JARD</t>
+  </si>
+  <si>
+    <t>PINO FEMEA</t>
+  </si>
+  <si>
+    <t>SUPORTE TV</t>
+  </si>
+  <si>
+    <t>GARIN SILICONE 050G INCOLOR COLMEIA 12 GARI</t>
+  </si>
+  <si>
+    <t>AGUARRAS</t>
+  </si>
+  <si>
+    <t>SENSOR PRESENÇA</t>
+  </si>
+  <si>
+    <t>AUMENTO TORNEIRA</t>
+  </si>
+  <si>
+    <t>ESTILETE</t>
+  </si>
+  <si>
+    <t>ADAPTADOR FURADEIRA P/ DISCO</t>
+  </si>
+  <si>
+    <t>ESTRELA LIGA FACIL</t>
+  </si>
+  <si>
+    <t>TORNEIRA CROMADO JARDIM ESFERA 1/2 FERTAK</t>
+  </si>
+  <si>
+    <t>FILTRO LINHA</t>
+  </si>
+  <si>
+    <t>CONTROLE TV</t>
+  </si>
+  <si>
+    <t>UNIPEGA SELANTE POLIURETANO</t>
+  </si>
+  <si>
+    <t>LIXA BOSCH AGUA</t>
+  </si>
+  <si>
+    <t>ELETRODUTO</t>
+  </si>
+  <si>
+    <t>VALVULA HYDRA</t>
+  </si>
+  <si>
+    <t>CHAVE SOQUETE</t>
+  </si>
+  <si>
+    <t>DISCO BORRACHA</t>
+  </si>
+  <si>
+    <t>TEE FORTLEV</t>
+  </si>
+  <si>
+    <t>GRAP TORNEIRA JARDIM ABS/PRETO 1/2</t>
+  </si>
+  <si>
+    <t>INTERNEED EXTENSÃO</t>
+  </si>
+  <si>
+    <t>GABINETE</t>
   </si>
   <si>
     <t xml:space="preserve">FIXA CUBA </t>
@@ -2653,31 +2658,31 @@
     <t xml:space="preserve">FERJA LIXA D AGUA </t>
   </si>
   <si>
-    <t xml:space="preserve">PENZEL TERM PREISOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARDEN JUNCAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARVAO MAKITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO FORTLEV LL MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXT ILUMI PLACA</t>
+    <t>PENZEL TERM PREISOL</t>
+  </si>
+  <si>
+    <t>GARDEN JUNCAO</t>
+  </si>
+  <si>
+    <t>REGUA</t>
+  </si>
+  <si>
+    <t>CARVAO MAKITA</t>
+  </si>
+  <si>
+    <t>COTOVELO FORTLEV LL MARROM</t>
+  </si>
+  <si>
+    <t>EXT ILUMI PLACA</t>
   </si>
   <si>
     <t xml:space="preserve">FIBRA ABRASIVA </t>
   </si>
   <si>
-    <t xml:space="preserve">SELATRINCAS GARIN BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIAPOL MASSA F12</t>
+    <t>SELATRINCAS GARIN BRANCO</t>
+  </si>
+  <si>
+    <t>VIAPOL MASSA F12</t>
   </si>
   <si>
     <r>
@@ -2697,585 +2702,588 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CONECTOR BORNE</t>
+      <t>CONECTOR BORNE</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ADAPTADOR GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VANGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO MAKITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO CORRER PLASTIK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINO ADAPTADOR  ROBUSTO ILUMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA ELETRICA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIXA ESPELHO CIBRA 400G BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIGRE GARFO BUCHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR GENERICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA PLASTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIZ DE LINHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROCA WIDEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE TIGRE MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEGATRON EXTENSAO TRIPOLAR</t>
+    <t>ADAPTADOR GARDEN</t>
+  </si>
+  <si>
+    <t>VANGA</t>
+  </si>
+  <si>
+    <t>PARAFUSO MAKITA</t>
+  </si>
+  <si>
+    <t>COTOVELO CORRER PLASTIK</t>
+  </si>
+  <si>
+    <t>PINO ADAPTADOR  ROBUSTO ILUMI</t>
+  </si>
+  <si>
+    <t>TORNEIRA ELETRICA</t>
+  </si>
+  <si>
+    <t>FIXA ESPELHO CIBRA 400G BRANCO</t>
+  </si>
+  <si>
+    <t>TIGRE GARFO BUCHA</t>
+  </si>
+  <si>
+    <t>CONECTOR GENERICO</t>
+  </si>
+  <si>
+    <t>VÁLVULA PLASTICO</t>
+  </si>
+  <si>
+    <t>GIZ DE LINHA</t>
+  </si>
+  <si>
+    <t>BROCA WIDEA</t>
+  </si>
+  <si>
+    <t>TEE TIGRE MARROM</t>
+  </si>
+  <si>
+    <t>MEGATRON EXTENSAO TRIPOLAR</t>
   </si>
   <si>
     <t xml:space="preserve">ESPONJA MAGICA 	</t>
   </si>
   <si>
-    <t xml:space="preserve">LIXA BOSCH D AGUA 80 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA RADIAL  CAIXA BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BASE REGISTRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FORMÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCO DIAMANTADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO TIGRE MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO NATICON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACO ALVEJADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA BOSCH D AGUA 100 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILUMI LUMINARIA TARTARUGA FERRO/VIDRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTRO PRESSAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACHAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO PONTAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLUG SHIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO DANEVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA BOSCH D AGUA 150 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEGATRON CABO PP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA HIDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESQUADRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO DE ESCOVAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA LUVA CORRER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PINO ADAPTADOR 2P T ROBUSTO ILUMI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA FLEXIVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISTEMA X ILUMI COTOVELO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA HYDRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCO SPED/INOX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA CORRER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO LINHA MEGATRON 5TOM BIVOLT PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AGULHA GRANDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE LAJE FIXO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REGISTRO GAVETA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERROTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDS PLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO CORRER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO LINHA MEGATRON 4TOM BIVOLT PRETO</t>
+    <t>LIXA BOSCH D AGUA 80 25</t>
+  </si>
+  <si>
+    <t>SISTEMA RADIAL  CAIXA BRANCO</t>
+  </si>
+  <si>
+    <t>BASE REGISTRO</t>
+  </si>
+  <si>
+    <t>FORMÃO</t>
+  </si>
+  <si>
+    <t>DISCO DIAMANTADO</t>
+  </si>
+  <si>
+    <t>COTOVELO TIGRE MARROM</t>
+  </si>
+  <si>
+    <t>EXTENSAO NATICON</t>
+  </si>
+  <si>
+    <t>SACO ALVEJADO</t>
+  </si>
+  <si>
+    <t>LIXA BOSCH D AGUA 100 25</t>
+  </si>
+  <si>
+    <t>ILUMI LUMINARIA TARTARUGA FERRO/VIDRO</t>
+  </si>
+  <si>
+    <t>REGISTRO PRESSAO</t>
+  </si>
+  <si>
+    <t>MACHAD</t>
+  </si>
+  <si>
+    <t>JOGO PONTAS</t>
+  </si>
+  <si>
+    <t>PLUG SHIVA</t>
+  </si>
+  <si>
+    <t>EXTENSAO DANEVA</t>
+  </si>
+  <si>
+    <t>LIXA BOSCH D AGUA 150 25</t>
+  </si>
+  <si>
+    <t>MEGATRON CABO PP</t>
+  </si>
+  <si>
+    <t>VÁLVULA HIDRA</t>
+  </si>
+  <si>
+    <t>ESQUADRO</t>
+  </si>
+  <si>
+    <t>JOGO DE ESCOVAS</t>
+  </si>
+  <si>
+    <t>KRONA LUVA CORRER</t>
+  </si>
+  <si>
+    <t>PINO ADAPTADOR 2P T ROBUSTO ILUMI</t>
+  </si>
+  <si>
+    <t>TORNEIRA FLEXIVEL</t>
+  </si>
+  <si>
+    <t>SISTEMA X ILUMI COTOVELO</t>
+  </si>
+  <si>
+    <t>VÁLVULA HYDRA</t>
+  </si>
+  <si>
+    <t>RODEL</t>
+  </si>
+  <si>
+    <t>DISCO SPED/INOX</t>
+  </si>
+  <si>
+    <t>LUVA CORRER</t>
+  </si>
+  <si>
+    <t>FILTRO LINHA MEGATRON 5TOM BIVOLT PRETO</t>
+  </si>
+  <si>
+    <t>AGULHA GRANDE</t>
+  </si>
+  <si>
+    <t>SUPORTE LAJE FIXO</t>
+  </si>
+  <si>
+    <t>REGISTRO GAVETA</t>
+  </si>
+  <si>
+    <t>SERROTE</t>
+  </si>
+  <si>
+    <t>SDS PLUS</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO CORRER</t>
+  </si>
+  <si>
+    <t>FILTRO LINHA MEGATRON 4TOM BIVOLT PRETO</t>
   </si>
   <si>
     <t xml:space="preserve">VIQUA TORNEIRA </t>
   </si>
   <si>
-    <t xml:space="preserve">THOMPSON CONECTOR 03 BORNE 10MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CENSI REPARO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE FIXA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDSPLUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPS CORRER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSÃO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA GAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THOMPSON CONECTOR 03 BORNE 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAPTADOR TANQUE GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE FENDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATEDOR ARGAMASSA CORTAG</t>
+    <t>THOMPSON CONECTOR 03 BORNE 10MM</t>
+  </si>
+  <si>
+    <t>CENSI REPARO</t>
+  </si>
+  <si>
+    <t>CHAVE FIXA</t>
+  </si>
+  <si>
+    <t>SDSPLUS</t>
+  </si>
+  <si>
+    <t>CAPS CORRER</t>
+  </si>
+  <si>
+    <t>EXTENSÃO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA GAS</t>
+  </si>
+  <si>
+    <t>THOMPSON CONECTOR 03 BORNE 16MM</t>
+  </si>
+  <si>
+    <t>ADAPTADOR TANQUE GARDEN</t>
+  </si>
+  <si>
+    <t>CHAVE FENDA</t>
+  </si>
+  <si>
+    <t>BATEDOR ARGAMASSA CORTAG</t>
   </si>
   <si>
     <t xml:space="preserve">LUVA SOLDAVEL </t>
   </si>
   <si>
-    <t xml:space="preserve">PLUG PORCELANA</t>
+    <t>PLUG PORCELANA</t>
   </si>
   <si>
     <t xml:space="preserve">ESPONJA FLASH </t>
   </si>
   <si>
-    <t xml:space="preserve">SUPORTE LAJE PE FIXO 30CM PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRA REPARO VÁLVULA</t>
+    <t>SUPORTE LAJE PE FIXO 30CM PRETO</t>
+  </si>
+  <si>
+    <t>HYDRA REPARO VÁLVULA</t>
   </si>
   <si>
     <t xml:space="preserve">MACANETA </t>
   </si>
   <si>
-    <t xml:space="preserve">MISTURADOR DE TINTA NYLON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA BUCHA REDUCAO LL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLUG RETANGULAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA MAQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXLUX LUMINARIA LED LINEAR 18W 60CM 6500K SLIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA HIDROMETRO SABESP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMINA SERRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISTURADOR DE TINTA COMPEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL LONGA CORRER PLASTICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILUMI PROLONGADOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IBIRA MANG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXLUX LUMINARIA LED LINEAR 36W 1 20M 6500K SLIM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNCAO METAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE COMBINADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARVAO FURADEIRA MAKITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO TIGRE LL B 3/4 X 90 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INJEREST SUPORTE LAJE PE FIXO 30CM PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA TANQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE BIELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE TIGRE LLL B 3/4 MARROM</t>
+    <t>MISTURADOR DE TINTA NYLON</t>
+  </si>
+  <si>
+    <t>KRONA BUCHA REDUCAO LL</t>
+  </si>
+  <si>
+    <t>PLUG RETANGULAR</t>
+  </si>
+  <si>
+    <t>TORNEIRA MAQ</t>
+  </si>
+  <si>
+    <t>FOXLUX LUMINARIA LED LINEAR 18W 60CM 6500K SLIM</t>
+  </si>
+  <si>
+    <t>CAIXA HIDROMETRO SABESP</t>
+  </si>
+  <si>
+    <t>LAMINA SERRA</t>
+  </si>
+  <si>
+    <t>MISTURADOR DE TINTA COMPEL</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL LONGA CORRER PLASTICO</t>
+  </si>
+  <si>
+    <t>ILUMI PROLONGADOR</t>
+  </si>
+  <si>
+    <t>IBIRA MANG</t>
+  </si>
+  <si>
+    <t>FOXLUX LUMINARIA LED LINEAR 36W 1 20M 6500K SLIM</t>
+  </si>
+  <si>
+    <t>JUNCAO METAL</t>
+  </si>
+  <si>
+    <t>CHAVE COMBINADA</t>
+  </si>
+  <si>
+    <t>CARVAO FURADEIRA MAKITA</t>
+  </si>
+  <si>
+    <t>COTOVELO TIGRE LL B 3/4 X 90 MARROM</t>
+  </si>
+  <si>
+    <t>INJEREST SUPORTE LAJE PE FIXO 30CM PRETO</t>
+  </si>
+  <si>
+    <t>VÁLVULA TANQUE</t>
+  </si>
+  <si>
+    <t>CHAVE BIELA</t>
+  </si>
+  <si>
+    <t>TEE TIGRE LLL B 3/4 MARROM</t>
   </si>
   <si>
     <t xml:space="preserve">CAMPAINHA </t>
   </si>
   <si>
-    <t xml:space="preserve">CONECTOR FERTAK PORCELANA 16MM BIF 8203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA MULTIUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE ALLEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA ADAPTADOR C/ FLANGE E ANEL 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROLE REMOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR FERTAK PORCELANA 10MM TRIF 8204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECANISMO ENTRADA UNIVERSAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE ESTRELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA ADAPTADOR C/ FLANGE E ANEL 11/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA VIQUA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONECTOR FERTAK PORCELANA 16MM TRIF 8205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLUKIT REPARO VALVULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA BOSCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA PLASTILIT LL B 3/4 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA HERC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE LAJE PP FUNDO FIXO 30CM PRETO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA MULT GORDURA CESTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA ACO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA PLASTILIT LL E 1 1/2 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPONJA MULTIUSO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADINHA C/ RABICHO REDY 107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAF CAIXA P/ HIDROMETRO PP SABESP NTS303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE CANHAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA PLASTILIT RR 3/4 BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALPHA TORNEIRA BICA MOVEL PAREDE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACABAMENTO REGISTRO ART METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE PHILLIPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA PLASTILIT RR 1/2 BRANCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HYDRAMOTION TORNEIRA MESA FLEXIVEL SILICONE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VÁLVULA AMERICANA METAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAQUIMETRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEE AZUL SHIVA 3/4 X 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALVA REGISTRO ALPHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE RODA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO FORTLEV LL H 3/4X45 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPONJA LIMPEZA PESADA FLASH LIMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMPERIO HIDRO ACABAMENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE DE GRIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO FORTLEV LL K 1 1/2X45 MARRON</t>
+    <t>CONECTOR FERTAK PORCELANA 16MM BIF 8203</t>
+  </si>
+  <si>
+    <t>VÁLVULA MULTIUSO</t>
+  </si>
+  <si>
+    <t>CHAVE ALLEN</t>
+  </si>
+  <si>
+    <t>KRONA ADAPTADOR C/ FLANGE E ANEL 3/4</t>
+  </si>
+  <si>
+    <t>CONTROLE REMOTO</t>
+  </si>
+  <si>
+    <t>CONECTOR FERTAK PORCELANA 10MM TRIF 8204</t>
+  </si>
+  <si>
+    <t>MECANISMO ENTRADA UNIVERSAL</t>
+  </si>
+  <si>
+    <t>CHAVE ESTRELA</t>
+  </si>
+  <si>
+    <t>KRONA ADAPTADOR C/ FLANGE E ANEL 11/2</t>
+  </si>
+  <si>
+    <t>TORNEIRA VIQUA</t>
+  </si>
+  <si>
+    <t>CONECTOR FERTAK PORCELANA 16MM TRIF 8205</t>
+  </si>
+  <si>
+    <t>BLUKIT REPARO VALVULA</t>
+  </si>
+  <si>
+    <t>SERRA BOSCH</t>
+  </si>
+  <si>
+    <t>LUVA PLASTILIT LL B 3/4 MARROM</t>
+  </si>
+  <si>
+    <t>TORNEIRA HERC</t>
+  </si>
+  <si>
+    <t>SUPORTE LAJE PP FUNDO FIXO 30CM PRETO</t>
+  </si>
+  <si>
+    <t>CAIXA MULT GORDURA CESTA</t>
+  </si>
+  <si>
+    <t>SERRA ACO</t>
+  </si>
+  <si>
+    <t>LUVA PLASTILIT LL E 1 1/2 MARROM</t>
+  </si>
+  <si>
+    <t>ESPONJA MULTIUSO</t>
+  </si>
+  <si>
+    <t>TOMADINHA C/ RABICHO REDY 107</t>
+  </si>
+  <si>
+    <t>TAF CAIXA P/ HIDROMETRO PP SABESP NTS303</t>
+  </si>
+  <si>
+    <t>CHAVE CANHAO</t>
+  </si>
+  <si>
+    <t>LUVA PLASTILIT RR 3/4 BRANCA</t>
+  </si>
+  <si>
+    <t>ALPHA TORNEIRA BICA MOVEL PAREDE</t>
+  </si>
+  <si>
+    <t>ACABAMENTO REGISTRO ART METAIS</t>
+  </si>
+  <si>
+    <t>CHAVE PHILLIPS</t>
+  </si>
+  <si>
+    <t>LUVA PLASTILIT RR 1/2 BRANCA</t>
+  </si>
+  <si>
+    <t>HYDRAMOTION TORNEIRA MESA FLEXIVEL SILICONE</t>
+  </si>
+  <si>
+    <t>VÁLVULA AMERICANA METAL</t>
+  </si>
+  <si>
+    <t>PAQUIMETRO</t>
+  </si>
+  <si>
+    <t>TEE AZUL SHIVA 3/4 X 1/2</t>
+  </si>
+  <si>
+    <t>SALVA REGISTRO ALPHA</t>
+  </si>
+  <si>
+    <t>CHAVE RODA</t>
+  </si>
+  <si>
+    <t>COTOVELO FORTLEV LL H 3/4X45 MARROM</t>
+  </si>
+  <si>
+    <t>ESPONJA LIMPEZA PESADA FLASH LIMP</t>
+  </si>
+  <si>
+    <t>IMPERIO HIDRO ACABAMENTO</t>
+  </si>
+  <si>
+    <t>CHAVE DE GRIFO</t>
+  </si>
+  <si>
+    <t>COTOVELO FORTLEV LL K 1 1/2X45 MARRON</t>
   </si>
   <si>
     <t xml:space="preserve">FRISO PORTA ALUMINIO </t>
   </si>
   <si>
-    <t xml:space="preserve">ACESSORIO CAIXA BLUKIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE INGLESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA FORTLEV LL B 3/4 X 90 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VENTILADOR DE MESA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACESSORIO CAIXA ASTRA ENT CAIXA ACOPLADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXADEIRA MANUAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO FORTLEV LL B 3/4X90 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATEDOR PORTA BOLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLUKIT KIT P/ CAIXA ACOPLADA UNIVERSAL SUPORTE BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE VIRAR FERRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COTOVELO FORTLEV LL E 1 1/2X90 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE BRASFORMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASTRA KIT P/ CAIXA ACOPLADA UNIVERSAL SUPORTE BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOMBA DE AR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CURVA FORTLEV LL E 1 1/2 X 90 MARROM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE P/ VARAO SIMPLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPARO CAIXA DESCARGA ACOPLADA NATURAL ASTRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOGO SOQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRONA PLUG 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE PIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRELHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARINHO PEDREIRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO ROSCA 3/4X1/2 50 KRONA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUPORTE PRIMETECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANEL DE VEDACAO FORTLEV 75MM ESGOTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERRA A R BOSCH BIMET 18D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL LONGA PLASTILIT 50 X 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAQUINA LAVAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 25MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARRINHO SERV GERAL ESFERA 150K P MACICO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO RR PLASTILIT A 3/4 X 1/2 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OVERTIME CHUVEIRINHO P/ TORNEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHAVE DE RODA CRUZ IMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL CURTA CORRER PLASTICO B 1 X 3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRIME TECH SUPORTE FORNO BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 32MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO RR CORRER PLASTIK 3/4X1/2 BRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA MAQUINA DE LAVAR ENTRADA 120MT IBIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA AUMENTO GARDEN 1/2 X3 /4 ZAMAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL CURTA FORTL A 3/4X1/2 MARRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA MAQUINA DE LAVAR ENTRADA 140MT IBIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO GARDEN 3/4 X 1/2 ZAMAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL LONGA FORT C 1 1/2 X3/4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA ENTRADA NOVA 14M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO CURTA 1/2 CROMADO GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA REDUCAO LL 11/2X3/4 LONGA KRONA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA ENTRADA NOVA 20M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO CROMADA MEDIA ZAMAC 1/2 GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA ENTRADA NOVA 20M CRISTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXTENSAO CROMADA LONGA ZAMAC 1/2 GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA B M FILTRO ACQUABIOS BRANCO QUADRISET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUCHA AUMENTO GARDEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TORNEIRA B M FILTRO ACQUABIOS PRETO QUADRISET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANGUEIRA TANQUINHO ENTRADA BRANCO FERE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SABONETEIRA HIDROLAR CROMADO 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARAO CORTINA STILLUS 150 BRC 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARAO CORTINA STILLUS 200 BRC 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODORIZADOR PURO AR LAVANDA 250ML</t>
+    <t>ACESSORIO CAIXA BLUKIT</t>
+  </si>
+  <si>
+    <t>CHAVE INGLESA</t>
+  </si>
+  <si>
+    <t>CURVA FORTLEV LL B 3/4 X 90 MARROM</t>
+  </si>
+  <si>
+    <t>VENTILADOR DE MESA</t>
+  </si>
+  <si>
+    <t>ACESSORIO CAIXA ASTRA ENT CAIXA ACOPLADA</t>
+  </si>
+  <si>
+    <t>LIXADEIRA MANUAL</t>
+  </si>
+  <si>
+    <t>COTOVELO FORTLEV LL B 3/4X90 MARROM</t>
+  </si>
+  <si>
+    <t>BATEDOR PORTA BOLA</t>
+  </si>
+  <si>
+    <t>BLUKIT KIT P/ CAIXA ACOPLADA UNIVERSAL SUPORTE BRANCO</t>
+  </si>
+  <si>
+    <t>CHAVE VIRAR FERRO</t>
+  </si>
+  <si>
+    <t>COTOVELO FORTLEV LL E 1 1/2X90 MARROM</t>
+  </si>
+  <si>
+    <t>SUPORTE BRASFORMA</t>
+  </si>
+  <si>
+    <t>ASTRA KIT P/ CAIXA ACOPLADA UNIVERSAL SUPORTE BRANCO</t>
+  </si>
+  <si>
+    <t>BOMBA DE AR</t>
+  </si>
+  <si>
+    <t>CURVA FORTLEV LL E 1 1/2 X 90 MARROM</t>
+  </si>
+  <si>
+    <t>SUPORTE P/ VARAO SIMPLES</t>
+  </si>
+  <si>
+    <t>REPARO CAIXA DESCARGA ACOPLADA NATURAL ASTRA</t>
+  </si>
+  <si>
+    <t>JOGO SOQUETE</t>
+  </si>
+  <si>
+    <t>KRONA PLUG 1/2</t>
+  </si>
+  <si>
+    <t>SUPORTE PIA</t>
+  </si>
+  <si>
+    <t>GRELHA</t>
+  </si>
+  <si>
+    <t>CARINHO PEDREIRO</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO ROSCA 3/4X1/2 50 KRONA</t>
+  </si>
+  <si>
+    <t>SUPORTE PRIMETECH</t>
+  </si>
+  <si>
+    <t>ANEL DE VEDACAO FORTLEV 75MM ESGOTO</t>
+  </si>
+  <si>
+    <t>SERRA A R BOSCH BIMET 18D</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL LONGA PLASTILIT 50 X 25</t>
+  </si>
+  <si>
+    <t>MAQUINA LAVAR</t>
+  </si>
+  <si>
+    <t>ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 25MM</t>
+  </si>
+  <si>
+    <t>CARRINHO SERV GERAL ESFERA 150K P MACICO</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO RR PLASTILIT A 3/4 X 1/2 BRANCO</t>
+  </si>
+  <si>
+    <t>OVERTIME CHUVEIRINHO P/ TORNEIRA</t>
+  </si>
+  <si>
+    <t>ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 50MM</t>
+  </si>
+  <si>
+    <t>CHAVE DE RODA CRUZ IMA</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL CURTA CORRER PLASTICO B 1 X 3/4</t>
+  </si>
+  <si>
+    <t>PRIME TECH SUPORTE FORNO BRANCO</t>
+  </si>
+  <si>
+    <t>ESTRELA VALVULA RETENÇÃO LL VERT/HOR PVC 32MM</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO RR CORRER PLASTIK 3/4X1/2 BRANCO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA MAQUINA DE LAVAR ENTRADA 120MT IBIRA</t>
+  </si>
+  <si>
+    <t>BUCHA AUMENTO GARDEN 1/2 X3 /4 ZAMAC</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL CURTA FORTL A 3/4X1/2 MARRO</t>
+  </si>
+  <si>
+    <t>MANGUEIRA MAQUINA DE LAVAR ENTRADA 140MT IBIRA</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO GARDEN 3/4 X 1/2 ZAMAC</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL LONGA FORT C 1 1/2 X3/4</t>
+  </si>
+  <si>
+    <t>MANGUEIRA ENTRADA NOVA 14M</t>
+  </si>
+  <si>
+    <t>EXTENSAO CURTA 1/2 CROMADO GARDEN</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO LL 11/2X3/4 LONGA KRONA</t>
+  </si>
+  <si>
+    <t>MANGUEIRA ENTRADA NOVA 20M</t>
+  </si>
+  <si>
+    <t>EXTENSAO CROMADA MEDIA ZAMAC 1/2 GARDEN</t>
+  </si>
+  <si>
+    <t>MANGUEIRA ENTRADA NOVA 20M CRISTAL</t>
+  </si>
+  <si>
+    <t>EXTENSAO CROMADA LONGA ZAMAC 1/2 GARDEN</t>
+  </si>
+  <si>
+    <t>TORNEIRA B M FILTRO ACQUABIOS BRANCO QUADRISET</t>
+  </si>
+  <si>
+    <t>BUCHA AUMENTO GARDEN</t>
+  </si>
+  <si>
+    <t>TORNEIRA B M FILTRO ACQUABIOS PRETO QUADRISET</t>
+  </si>
+  <si>
+    <t>MANGUEIRA TANQUINHO ENTRADA BRANCO FERE</t>
+  </si>
+  <si>
+    <t>SABONETEIRA HIDROLAR CROMADO 2025</t>
+  </si>
+  <si>
+    <t>VARAO CORTINA STILLUS 150 BRC 01</t>
+  </si>
+  <si>
+    <t>VARAO CORTINA STILLUS 200 BRC 01</t>
+  </si>
+  <si>
+    <t>ODORIZADOR PURO AR LAVANDA 250ML</t>
+  </si>
+  <si>
+    <t>BUCHA REDUCAO RR PLASTILIT A</t>
+  </si>
+  <si>
+    <t>SERRA A R STARRETT TUBO/BIMET 24D</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -3283,22 +3291,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -3319,7 +3312,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -3335,7 +3328,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -3343,131 +3336,91 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -3520,53 +3473,52 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AF91"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="41.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="52.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="51.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="50.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="66.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="33.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="25.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="45.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="64.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="40.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="53.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="47.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="42.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="39.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="22.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="24.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="21.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="25.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="51.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="47.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="52.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="59.14"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="33" style="1" width="11.57"/>
+    <col min="1" max="1" width="44.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="52" style="1" customWidth="1"/>
+    <col min="4" max="4" width="52.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27" style="1" customWidth="1"/>
+    <col min="7" max="7" width="51.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="66.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="33.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="45.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="64.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="41.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="53.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="47.140625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="42.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="18" style="1" customWidth="1"/>
+    <col min="20" max="20" width="39.28515625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="22.140625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="24.28515625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.5703125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="55" style="1" customWidth="1"/>
+    <col min="26" max="26" width="51.42578125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="37.5703125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="47.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="52.28515625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="34" style="1" customWidth="1"/>
+    <col min="31" max="31" width="37" style="1" customWidth="1"/>
+    <col min="32" max="32" width="59.140625" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3664,7 +3616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
@@ -3762,7 +3714,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>64</v>
       </c>
@@ -3860,7 +3812,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:32" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>96</v>
       </c>
@@ -3958,7 +3910,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>128</v>
       </c>
@@ -4053,7 +4005,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>159</v>
       </c>
@@ -4148,7 +4100,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>190</v>
       </c>
@@ -4240,7 +4192,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>219</v>
       </c>
@@ -4329,7 +4281,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>247</v>
       </c>
@@ -4418,7 +4370,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>276</v>
       </c>
@@ -4504,7 +4456,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:32" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>304</v>
       </c>
@@ -4584,7 +4536,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>330</v>
       </c>
@@ -4661,7 +4613,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>355</v>
       </c>
@@ -4735,7 +4687,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
         <v>379</v>
       </c>
@@ -4803,7 +4755,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
         <v>401</v>
       </c>
@@ -4871,7 +4823,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:32" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>423</v>
       </c>
@@ -4936,7 +4888,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>443</v>
       </c>
@@ -4992,7 +4944,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>461</v>
       </c>
@@ -5048,7 +5000,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>221</v>
       </c>
@@ -5104,7 +5056,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>496</v>
       </c>
@@ -5160,7 +5112,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="2:32" ht="15" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>514</v>
       </c>
@@ -5216,7 +5168,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>531</v>
       </c>
@@ -5269,7 +5221,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="2:32" ht="15" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>547</v>
       </c>
@@ -5319,7 +5271,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>563</v>
       </c>
@@ -5369,7 +5321,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>579</v>
       </c>
@@ -5419,7 +5371,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>594</v>
       </c>
@@ -5470,7 +5422,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>609</v>
       </c>
@@ -5520,7 +5472,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>625</v>
       </c>
@@ -5570,7 +5522,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C30" s="4" t="s">
         <v>640</v>
       </c>
@@ -5617,7 +5569,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>655</v>
       </c>
@@ -5661,7 +5613,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="2:32" ht="15" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
         <v>669</v>
       </c>
@@ -5705,7 +5657,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>683</v>
       </c>
@@ -5746,7 +5698,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>696</v>
       </c>
@@ -5784,7 +5736,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>707</v>
       </c>
@@ -5822,7 +5774,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" spans="3:32" ht="15" x14ac:dyDescent="0.25">
       <c r="C36" s="1" t="s">
         <v>719</v>
       </c>
@@ -5860,7 +5812,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C37" s="1" t="s">
         <v>731</v>
       </c>
@@ -5895,7 +5847,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>742</v>
       </c>
@@ -5930,7 +5882,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>753</v>
       </c>
@@ -5965,7 +5917,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>764</v>
       </c>
@@ -6000,7 +5952,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>775</v>
       </c>
@@ -6035,7 +5987,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>786</v>
       </c>
@@ -6070,7 +6022,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>797</v>
       </c>
@@ -6105,7 +6057,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" spans="3:32" x14ac:dyDescent="0.2">
       <c r="D44" s="1" t="s">
         <v>808</v>
       </c>
@@ -6137,7 +6089,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" spans="3:32" x14ac:dyDescent="0.2">
       <c r="D45" s="1" t="s">
         <v>818</v>
       </c>
@@ -6169,7 +6121,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" spans="3:32" x14ac:dyDescent="0.2">
       <c r="D46" s="1" t="s">
         <v>828</v>
       </c>
@@ -6201,7 +6153,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" spans="3:32" x14ac:dyDescent="0.2">
       <c r="D47" s="1" t="s">
         <v>838</v>
       </c>
@@ -6230,7 +6182,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" spans="3:32" ht="15" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
         <v>847</v>
       </c>
@@ -6259,7 +6211,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
         <v>856</v>
       </c>
@@ -6288,7 +6240,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D50" s="1" t="s">
         <v>865</v>
       </c>
@@ -6314,7 +6266,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D51" s="1" t="s">
         <v>873</v>
       </c>
@@ -6340,7 +6292,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D52" s="1" t="s">
         <v>533</v>
       </c>
@@ -6366,7 +6318,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
         <v>888</v>
       </c>
@@ -6389,7 +6341,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
         <v>895</v>
       </c>
@@ -6412,7 +6364,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D55" s="6" t="s">
         <v>902</v>
       </c>
@@ -6435,7 +6387,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D56" s="1" t="s">
         <v>909</v>
       </c>
@@ -6458,7 +6410,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D57" s="1" t="s">
         <v>916</v>
       </c>
@@ -6481,7 +6433,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D58" s="1" t="s">
         <v>923</v>
       </c>
@@ -6504,7 +6456,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D59" s="1" t="s">
         <v>930</v>
       </c>
@@ -6524,7 +6476,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
         <v>358</v>
       </c>
@@ -6537,11 +6489,14 @@
       <c r="L60" s="1" t="s">
         <v>938</v>
       </c>
+      <c r="N60" t="s">
+        <v>1041</v>
+      </c>
       <c r="Z60" s="1" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" spans="4:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D61" s="4" t="s">
         <v>940</v>
       </c>
@@ -6558,7 +6513,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" spans="4:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D62" s="1" t="s">
         <v>945</v>
       </c>
@@ -6575,7 +6530,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" spans="4:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D63" s="1" t="s">
         <v>950</v>
       </c>
@@ -6592,7 +6547,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" spans="4:32" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
         <v>955</v>
       </c>
@@ -6609,7 +6564,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
         <v>960</v>
       </c>
@@ -6626,7 +6581,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D66" s="4" t="s">
         <v>965</v>
       </c>
@@ -6640,7 +6595,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
         <v>969</v>
       </c>
@@ -6654,7 +6609,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
         <v>969</v>
       </c>
@@ -6668,7 +6623,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
         <v>976</v>
       </c>
@@ -6682,7 +6637,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D70" s="4" t="s">
         <v>980</v>
       </c>
@@ -6696,7 +6651,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
         <v>984</v>
       </c>
@@ -6710,7 +6665,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D72" s="4" t="s">
         <v>988</v>
       </c>
@@ -6724,7 +6679,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D73" s="1" t="s">
         <v>992</v>
       </c>
@@ -6738,7 +6693,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="4" t="s">
         <v>996</v>
       </c>
@@ -6752,7 +6707,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
         <v>1000</v>
       </c>
@@ -6766,7 +6721,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
         <v>1004</v>
       </c>
@@ -6780,7 +6735,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
         <v>1008</v>
       </c>
@@ -6791,10 +6746,10 @@
         <v>1010</v>
       </c>
       <c r="Z77" s="1" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="78" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D78" s="4" t="s">
         <v>1012</v>
       </c>
@@ -6805,10 +6760,10 @@
         <v>1014</v>
       </c>
       <c r="Z78" s="1" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="79" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D79" s="4" t="s">
         <v>1016</v>
       </c>
@@ -6816,10 +6771,10 @@
         <v>1017</v>
       </c>
       <c r="Z79" s="1" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="80" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D80" s="1" t="s">
         <v>1019</v>
       </c>
@@ -6827,10 +6782,10 @@
         <v>1020</v>
       </c>
       <c r="Z80" s="1" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="81" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D81" s="1" t="s">
         <v>1022</v>
       </c>
@@ -6838,10 +6793,10 @@
         <v>1023</v>
       </c>
       <c r="Z81" s="1" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="82" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D82" s="1" t="s">
         <v>1025</v>
       </c>
@@ -6849,18 +6804,21 @@
         <v>1026</v>
       </c>
       <c r="Z82" s="1" t="s">
-        <v>1027</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="83" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D83" s="1" t="s">
         <v>1028</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>1029</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="Z83" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="84" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D84" s="1" t="s">
         <v>1030</v>
       </c>
@@ -6868,7 +6826,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D85" s="1" t="s">
         <v>1032</v>
       </c>
@@ -6876,41 +6834,40 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D86" s="1" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D87" s="1" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D88" s="1" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D89" s="1" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D90" s="1" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" spans="4:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D91" s="1" t="s">
         <v>1039</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
